--- a/database/event/8261/event_8261_evp_summary.xlsx
+++ b/database/event/8261/event_8261_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.0526</v>
+        <v>12.1193</v>
       </c>
       <c r="C2" t="n">
-        <v>8.259600000000001</v>
+        <v>8.305300000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4476</v>
+        <v>4.3844</v>
       </c>
       <c r="E2" t="n">
-        <v>12.0526</v>
+        <v>12.1193</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2905</v>
+        <v>5.3572</v>
       </c>
       <c r="G2" t="n">
         <v>6.7621</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9924</v>
+        <v>6.097</v>
       </c>
       <c r="I2" t="n">
-        <v>6.0203</v>
+        <v>6.1484</v>
       </c>
       <c r="J2" t="n">
         <v>9.2691</v>
@@ -529,7 +529,7 @@
         <v>212</v>
       </c>
       <c r="M2" t="n">
-        <v>15.2894</v>
+        <v>15.4175</v>
       </c>
       <c r="N2" t="n">
         <v>394</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3267</v>
+        <v>7.4859</v>
       </c>
       <c r="C3" t="n">
-        <v>5.0209</v>
+        <v>5.13</v>
       </c>
       <c r="D3" t="n">
         <v>2.5385</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3267</v>
+        <v>7.4859</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3743</v>
+        <v>4.2898</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9524</v>
+        <v>3.1961</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3743</v>
+        <v>4.4233</v>
       </c>
       <c r="I3" t="n">
-        <v>3.39</v>
+        <v>4.4233</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9524</v>
+        <v>3.1961</v>
       </c>
       <c r="K3" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="L3" t="n">
-        <v>212</v>
+        <v>85</v>
       </c>
       <c r="M3" t="n">
-        <v>7.3424</v>
+        <v>7.619400000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>394</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.2441</v>
+        <v>7.3141</v>
       </c>
       <c r="C4" t="n">
-        <v>4.9643</v>
+        <v>5.0123</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5051</v>
+        <v>2.47</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2441</v>
+        <v>7.3141</v>
       </c>
       <c r="F4" t="n">
-        <v>4.048</v>
+        <v>3.3617</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1961</v>
+        <v>3.9524</v>
       </c>
       <c r="H4" t="n">
-        <v>4.048</v>
+        <v>3.3617</v>
       </c>
       <c r="I4" t="n">
-        <v>4.048</v>
+        <v>3.39</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1961</v>
+        <v>3.9524</v>
       </c>
       <c r="K4" t="n">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="L4" t="n">
-        <v>85</v>
+        <v>212</v>
       </c>
       <c r="M4" t="n">
-        <v>7.2441</v>
+        <v>7.3424</v>
       </c>
       <c r="N4" t="n">
-        <v>291</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.4765</v>
+        <v>6.5718</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4383</v>
+        <v>4.5036</v>
       </c>
       <c r="D5" t="n">
-        <v>2.195</v>
+        <v>2.1743</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4765</v>
+        <v>6.5718</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1853</v>
+        <v>4.2806</v>
       </c>
       <c r="G5" t="n">
         <v>2.2912</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2596</v>
+        <v>4.409</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2596</v>
+        <v>4.409</v>
       </c>
       <c r="J5" t="n">
         <v>2.2912</v>
@@ -667,7 +667,7 @@
         <v>121</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5508</v>
+        <v>6.7002</v>
       </c>
       <c r="N5" t="n">
         <v>353</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9543</v>
+        <v>6.1499</v>
       </c>
       <c r="C6" t="n">
-        <v>4.0804</v>
+        <v>4.2145</v>
       </c>
       <c r="D6" t="n">
-        <v>1.984</v>
+        <v>2.0062</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9543</v>
+        <v>6.1499</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6021</v>
+        <v>4.8446</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3522</v>
+        <v>1.3053</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6021</v>
+        <v>5.2932</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6021</v>
+        <v>5.2932</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3522</v>
+        <v>1.3053</v>
       </c>
       <c r="K6" t="n">
-        <v>232</v>
+        <v>101</v>
       </c>
       <c r="L6" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>5.9543</v>
+        <v>6.5985</v>
       </c>
       <c r="N6" t="n">
-        <v>353</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6261</v>
+        <v>5.9543</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8555</v>
+        <v>4.0804</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8515</v>
+        <v>1.9283</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6261</v>
+        <v>5.9543</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6274</v>
+        <v>3.6021</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9987</v>
+        <v>2.3522</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6274</v>
+        <v>3.6021</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6274</v>
+        <v>3.6021</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9987</v>
+        <v>2.3522</v>
       </c>
       <c r="K7" t="n">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="L7" t="n">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="M7" t="n">
-        <v>5.6261</v>
+        <v>5.9543</v>
       </c>
       <c r="N7" t="n">
-        <v>376</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5654</v>
+        <v>5.6261</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8139</v>
+        <v>3.8555</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8269</v>
+        <v>1.7975</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5654</v>
+        <v>5.6261</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2601</v>
+        <v>2.6274</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3053</v>
+        <v>2.9987</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3767</v>
+        <v>2.6274</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3767</v>
+        <v>2.6274</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3053</v>
+        <v>2.9987</v>
       </c>
       <c r="K8" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="L8" t="n">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="M8" t="n">
-        <v>5.681999999999999</v>
+        <v>5.6261</v>
       </c>
       <c r="N8" t="n">
-        <v>144</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.9376</v>
+        <v>5.1315</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3837</v>
+        <v>3.5166</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5733</v>
+        <v>1.6005</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9376</v>
+        <v>5.1315</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1151</v>
+        <v>4.309</v>
       </c>
       <c r="G9" t="n">
         <v>0.8225</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1495</v>
+        <v>4.4534</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1688</v>
+        <v>4.4909</v>
       </c>
       <c r="J9" t="n">
         <v>0.8225</v>
@@ -851,7 +851,7 @@
         <v>70</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9913</v>
+        <v>5.3134</v>
       </c>
       <c r="N9" t="n">
         <v>232</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.8334</v>
+        <v>5.1229</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3123</v>
+        <v>3.5107</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5312</v>
+        <v>1.5971</v>
       </c>
       <c r="E10" t="n">
-        <v>4.8334</v>
+        <v>5.1229</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2193</v>
+        <v>2.5089</v>
       </c>
       <c r="G10" t="n">
         <v>2.614</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2193</v>
+        <v>2.5089</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2193</v>
+        <v>2.5089</v>
       </c>
       <c r="J10" t="n">
         <v>2.614</v>
@@ -897,7 +897,7 @@
         <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>4.833299999999999</v>
+        <v>5.1229</v>
       </c>
       <c r="N10" t="n">
         <v>291</v>
@@ -916,7 +916,7 @@
         <v>3.2083</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4699</v>
+        <v>1.4212</v>
       </c>
       <c r="E11" t="n">
         <v>4.6816</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.638</v>
+        <v>4.6269</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1784</v>
+        <v>3.1708</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4523</v>
+        <v>1.3994</v>
       </c>
       <c r="E12" t="n">
-        <v>4.638</v>
+        <v>4.6269</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4504</v>
+        <v>4.4393</v>
       </c>
       <c r="G12" t="n">
         <v>0.1876</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6751</v>
+        <v>4.6577</v>
       </c>
       <c r="I12" t="n">
         <v>4.6969</v>
@@ -1008,7 +1008,7 @@
         <v>3.009</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3524</v>
+        <v>1.3054</v>
       </c>
       <c r="E13" t="n">
         <v>4.3908</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8217</v>
+        <v>3.9837</v>
       </c>
       <c r="C14" t="n">
-        <v>2.619</v>
+        <v>2.73</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1225</v>
+        <v>1.1432</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8217</v>
+        <v>3.9837</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1035</v>
+        <v>4.2826</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2818</v>
+        <v>-0.2989</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1313</v>
+        <v>4.412</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1313</v>
+        <v>4.412</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2818</v>
+        <v>-0.2989</v>
       </c>
       <c r="K14" t="n">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="L14" t="n">
-        <v>219</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8495</v>
+        <v>4.1131</v>
       </c>
       <c r="N14" t="n">
-        <v>376</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7551</v>
+        <v>3.9095</v>
       </c>
       <c r="C15" t="n">
-        <v>2.5733</v>
+        <v>2.6792</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0956</v>
+        <v>1.1136</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7551</v>
+        <v>3.9095</v>
       </c>
       <c r="F15" t="n">
-        <v>4.054</v>
+        <v>4.1913</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2989</v>
+        <v>-0.2818</v>
       </c>
       <c r="H15" t="n">
-        <v>4.054</v>
+        <v>4.269</v>
       </c>
       <c r="I15" t="n">
-        <v>4.054</v>
+        <v>4.269</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2989</v>
+        <v>-0.2818</v>
       </c>
       <c r="K15" t="n">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="L15" t="n">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7551</v>
+        <v>3.9872</v>
       </c>
       <c r="N15" t="n">
-        <v>291</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5711</v>
+        <v>3.8446</v>
       </c>
       <c r="C16" t="n">
-        <v>2.4473</v>
+        <v>2.6347</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0213</v>
+        <v>1.0878</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5711</v>
+        <v>3.8446</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1002</v>
+        <v>3.3737</v>
       </c>
       <c r="G16" t="n">
         <v>0.4709</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1002</v>
+        <v>3.3737</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1146</v>
+        <v>3.4021</v>
       </c>
       <c r="J16" t="n">
         <v>0.4709</v>
@@ -1173,7 +1173,7 @@
         <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5855</v>
+        <v>3.873</v>
       </c>
       <c r="N16" t="n">
         <v>268</v>
@@ -1192,7 +1192,7 @@
         <v>2.4003</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9936</v>
+        <v>0.9515</v>
       </c>
       <c r="E17" t="n">
         <v>3.5026</v>
@@ -1228,461 +1228,461 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3916</v>
+        <v>3.4761</v>
       </c>
       <c r="C18" t="n">
-        <v>2.3242</v>
+        <v>2.3821</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9488</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3916</v>
+        <v>3.4761</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1057</v>
+        <v>4.5262</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2859</v>
+        <v>-1.0501</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1057</v>
+        <v>4.7941</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1057</v>
+        <v>4.7941</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2859</v>
+        <v>-1.0501</v>
       </c>
       <c r="K18" t="n">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="L18" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3916</v>
+        <v>3.744</v>
       </c>
       <c r="N18" t="n">
-        <v>353</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3608</v>
+        <v>3.3916</v>
       </c>
       <c r="C19" t="n">
-        <v>2.3031</v>
+        <v>2.3242</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9363</v>
+        <v>0.9073</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3608</v>
+        <v>3.3916</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2331</v>
+        <v>2.1057</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1277</v>
+        <v>1.2859</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2331</v>
+        <v>2.1057</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2331</v>
+        <v>2.1057</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1277</v>
+        <v>1.2859</v>
       </c>
       <c r="K19" t="n">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="L19" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3608</v>
+        <v>3.3916</v>
       </c>
       <c r="N19" t="n">
-        <v>192</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3082</v>
+        <v>3.3608</v>
       </c>
       <c r="C20" t="n">
-        <v>2.2671</v>
+        <v>2.3031</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9151</v>
+        <v>0.895</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3082</v>
+        <v>3.3608</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0564</v>
+        <v>3.2331</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2518</v>
+        <v>0.1277</v>
       </c>
       <c r="H20" t="n">
-        <v>3.0564</v>
+        <v>3.2331</v>
       </c>
       <c r="I20" t="n">
-        <v>3.0706</v>
+        <v>3.2331</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2518</v>
+        <v>0.1277</v>
       </c>
       <c r="K20" t="n">
-        <v>221</v>
+        <v>143</v>
       </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3224</v>
+        <v>3.3608</v>
       </c>
       <c r="N20" t="n">
-        <v>268</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.2806</v>
+        <v>3.2968</v>
       </c>
       <c r="C21" t="n">
-        <v>2.2482</v>
+        <v>2.2593</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9039</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2806</v>
+        <v>3.2968</v>
       </c>
       <c r="F21" t="n">
-        <v>4.3307</v>
+        <v>3.045</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0501</v>
+        <v>0.2518</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4875</v>
+        <v>3.045</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4875</v>
+        <v>3.0706</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0501</v>
+        <v>0.2518</v>
       </c>
       <c r="K21" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="L21" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4374</v>
+        <v>3.3224</v>
       </c>
       <c r="N21" t="n">
-        <v>291</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.0022</v>
+        <v>3.2043</v>
       </c>
       <c r="C22" t="n">
-        <v>2.0574</v>
+        <v>2.1959</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7915</v>
+        <v>0.8327</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0022</v>
+        <v>3.2043</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9593</v>
+        <v>4.1567</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9615</v>
+        <v>-0.9524</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9593</v>
+        <v>4.2146</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9638</v>
+        <v>4.2146</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9615</v>
+        <v>-0.9524</v>
       </c>
       <c r="K22" t="n">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="L22" t="n">
-        <v>212</v>
+        <v>43</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9977</v>
+        <v>3.2622</v>
       </c>
       <c r="N22" t="n">
-        <v>394</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.7922</v>
+        <v>3.196</v>
       </c>
       <c r="C23" t="n">
-        <v>1.9135</v>
+        <v>2.1902</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7066</v>
+        <v>0.8294</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7922</v>
+        <v>3.196</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9244</v>
+        <v>3.196</v>
       </c>
       <c r="G23" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9244</v>
+        <v>3.196</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9244</v>
+        <v>3.196</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>232</v>
+        <v>165</v>
       </c>
       <c r="L23" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7922</v>
+        <v>3.196</v>
       </c>
       <c r="N23" t="n">
-        <v>353</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7822</v>
+        <v>3.0907</v>
       </c>
       <c r="C24" t="n">
-        <v>1.9066</v>
+        <v>2.118</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7026</v>
+        <v>0.7874</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7822</v>
+        <v>3.0907</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4007</v>
+        <v>3.0907</v>
       </c>
       <c r="G24" t="n">
-        <v>1.3815</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4007</v>
+        <v>3.0907</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4007</v>
+        <v>3.0907</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3815</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="L24" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7822</v>
+        <v>3.0907</v>
       </c>
       <c r="N24" t="n">
-        <v>376</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7449</v>
+        <v>3.0563</v>
       </c>
       <c r="C25" t="n">
-        <v>1.8811</v>
+        <v>2.0945</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6875</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7449</v>
+        <v>3.0563</v>
       </c>
       <c r="F25" t="n">
-        <v>3.6973</v>
+        <v>3.0563</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9524</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.6973</v>
+        <v>3.0563</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6973</v>
+        <v>3.0563</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9524</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="L25" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7449</v>
+        <v>3.0563</v>
       </c>
       <c r="N25" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.5793</v>
+        <v>3.0057</v>
       </c>
       <c r="C26" t="n">
-        <v>1.7676</v>
+        <v>2.0598</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6206</v>
+        <v>0.7536</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5793</v>
+        <v>3.0057</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2867</v>
+        <v>-0.9558</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2926</v>
+        <v>3.9615</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2867</v>
+        <v>-0.9558</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2973</v>
+        <v>-0.9638</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2926</v>
+        <v>3.9615</v>
       </c>
       <c r="K26" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="M26" t="n">
-        <v>2.5899</v>
+        <v>2.9977</v>
       </c>
       <c r="N26" t="n">
-        <v>232</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.5338</v>
+        <v>2.859</v>
       </c>
       <c r="C27" t="n">
-        <v>1.7364</v>
+        <v>1.9593</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6022</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5338</v>
+        <v>2.859</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5338</v>
+        <v>1.4775</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.3815</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5338</v>
+        <v>1.4775</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5338</v>
+        <v>1.4775</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.3815</v>
       </c>
       <c r="K27" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5338</v>
+        <v>2.859</v>
       </c>
       <c r="N27" t="n">
-        <v>159</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4611</v>
+        <v>2.8324</v>
       </c>
       <c r="C28" t="n">
-        <v>1.6866</v>
+        <v>1.941</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5729</v>
+        <v>0.6845</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4611</v>
+        <v>2.8324</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4611</v>
+        <v>2.8324</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4611</v>
+        <v>2.8324</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4611</v>
+        <v>2.8324</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.4611</v>
+        <v>2.8324</v>
       </c>
       <c r="N28" t="n">
         <v>180</v>
@@ -1734,415 +1734,415 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.4428</v>
+        <v>2.7922</v>
       </c>
       <c r="C29" t="n">
-        <v>1.674</v>
+        <v>1.9135</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5655</v>
+        <v>0.6685</v>
       </c>
       <c r="E29" t="n">
-        <v>2.4428</v>
+        <v>2.7922</v>
       </c>
       <c r="F29" t="n">
-        <v>2.4428</v>
+        <v>-0.9244</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="H29" t="n">
-        <v>2.4428</v>
+        <v>-0.9244</v>
       </c>
       <c r="I29" t="n">
-        <v>2.4428</v>
+        <v>-0.9244</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="K29" t="n">
-        <v>120</v>
+        <v>232</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M29" t="n">
-        <v>2.4428</v>
+        <v>2.7922</v>
       </c>
       <c r="N29" t="n">
-        <v>120</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.3943</v>
+        <v>2.6056</v>
       </c>
       <c r="C30" t="n">
-        <v>1.6408</v>
+        <v>1.7856</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5942</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3943</v>
+        <v>2.6056</v>
       </c>
       <c r="F30" t="n">
-        <v>2.3943</v>
+        <v>3.3564</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.7508</v>
       </c>
       <c r="H30" t="n">
-        <v>2.3943</v>
+        <v>3.3564</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3943</v>
+        <v>3.3564</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.7508</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>2.3943</v>
+        <v>2.6056</v>
       </c>
       <c r="N30" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3159</v>
+        <v>2.5708</v>
       </c>
       <c r="C31" t="n">
-        <v>1.5871</v>
+        <v>1.7618</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5142</v>
+        <v>0.5803</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3159</v>
+        <v>2.5708</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3159</v>
+        <v>2.2782</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.2926</v>
       </c>
       <c r="H31" t="n">
-        <v>2.3159</v>
+        <v>2.2782</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3159</v>
+        <v>2.2973</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2926</v>
       </c>
       <c r="K31" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M31" t="n">
-        <v>2.3159</v>
+        <v>2.5899</v>
       </c>
       <c r="N31" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2802</v>
+        <v>2.4428</v>
       </c>
       <c r="C32" t="n">
-        <v>1.5626</v>
+        <v>1.674</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4998</v>
+        <v>0.5293</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2802</v>
+        <v>2.4428</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2802</v>
+        <v>2.4428</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2802</v>
+        <v>2.4428</v>
       </c>
       <c r="I32" t="n">
-        <v>2.2802</v>
+        <v>2.4428</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.2802</v>
+        <v>2.4428</v>
       </c>
       <c r="N32" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.2653</v>
+        <v>2.3943</v>
       </c>
       <c r="C33" t="n">
-        <v>1.5524</v>
+        <v>1.6408</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4938</v>
+        <v>0.51</v>
       </c>
       <c r="E33" t="n">
-        <v>2.2653</v>
+        <v>2.3943</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2653</v>
+        <v>2.3943</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2653</v>
+        <v>2.3943</v>
       </c>
       <c r="I33" t="n">
-        <v>2.2653</v>
+        <v>2.3943</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.2653</v>
+        <v>2.3943</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.2357</v>
+        <v>2.363</v>
       </c>
       <c r="C34" t="n">
-        <v>1.5321</v>
+        <v>1.6193</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4818</v>
+        <v>0.4975</v>
       </c>
       <c r="E34" t="n">
-        <v>2.2357</v>
+        <v>2.363</v>
       </c>
       <c r="F34" t="n">
-        <v>2.2357</v>
+        <v>2.363</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.2357</v>
+        <v>2.363</v>
       </c>
       <c r="I34" t="n">
-        <v>2.2357</v>
+        <v>2.363</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.2357</v>
+        <v>2.363</v>
       </c>
       <c r="N34" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.2333</v>
+        <v>2.3501</v>
       </c>
       <c r="C35" t="n">
-        <v>1.5305</v>
+        <v>1.6105</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4808</v>
+        <v>0.4924</v>
       </c>
       <c r="E35" t="n">
-        <v>2.2333</v>
+        <v>2.3501</v>
       </c>
       <c r="F35" t="n">
-        <v>2.2333</v>
+        <v>2.3501</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.2333</v>
+        <v>2.3501</v>
       </c>
       <c r="I35" t="n">
-        <v>2.2333</v>
+        <v>2.3501</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.2333</v>
+        <v>2.3501</v>
       </c>
       <c r="N35" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.2104</v>
+        <v>2.3159</v>
       </c>
       <c r="C36" t="n">
-        <v>1.5148</v>
+        <v>1.5871</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4716</v>
+        <v>0.4787</v>
       </c>
       <c r="E36" t="n">
-        <v>2.2104</v>
+        <v>2.3159</v>
       </c>
       <c r="F36" t="n">
-        <v>2.5901</v>
+        <v>2.3159</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3797</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.5901</v>
+        <v>2.3159</v>
       </c>
       <c r="I36" t="n">
-        <v>2.6022</v>
+        <v>2.3159</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3797</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="L36" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.2225</v>
+        <v>2.3159</v>
       </c>
       <c r="N36" t="n">
-        <v>268</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.1611</v>
+        <v>2.2008</v>
       </c>
       <c r="C37" t="n">
-        <v>1.481</v>
+        <v>1.5082</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4517</v>
+        <v>0.4329</v>
       </c>
       <c r="E37" t="n">
-        <v>2.1611</v>
+        <v>2.2008</v>
       </c>
       <c r="F37" t="n">
-        <v>2.9119</v>
+        <v>2.5805</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7508</v>
+        <v>-0.3797</v>
       </c>
       <c r="H37" t="n">
-        <v>2.9119</v>
+        <v>2.5805</v>
       </c>
       <c r="I37" t="n">
-        <v>2.9119</v>
+        <v>2.6022</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7508</v>
+        <v>-0.3797</v>
       </c>
       <c r="K37" t="n">
-        <v>143</v>
+        <v>221</v>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M37" t="n">
-        <v>2.1611</v>
+        <v>2.2225</v>
       </c>
       <c r="N37" t="n">
-        <v>192</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>1.4728</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4468</v>
+        <v>0.4123</v>
       </c>
       <c r="E38" t="n">
         <v>2.1491</v>
@@ -2204,7 +2204,7 @@
         <v>1.4694</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4448</v>
+        <v>0.4103</v>
       </c>
       <c r="E39" t="n">
         <v>2.1442</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.0899</v>
+        <v>2.1101</v>
       </c>
       <c r="C40" t="n">
-        <v>1.4322</v>
+        <v>1.446</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4229</v>
+        <v>0.3968</v>
       </c>
       <c r="E40" t="n">
-        <v>2.0899</v>
+        <v>2.1101</v>
       </c>
       <c r="F40" t="n">
-        <v>2.0899</v>
+        <v>2.1101</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.0899</v>
+        <v>2.1101</v>
       </c>
       <c r="I40" t="n">
-        <v>2.0899</v>
+        <v>2.1101</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.0899</v>
+        <v>2.1101</v>
       </c>
       <c r="N40" t="n">
         <v>107</v>
@@ -2286,952 +2286,952 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.9956</v>
+        <v>2.0473</v>
       </c>
       <c r="C41" t="n">
-        <v>1.3676</v>
+        <v>1.403</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3848</v>
+        <v>0.3717</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9956</v>
+        <v>2.0473</v>
       </c>
       <c r="F41" t="n">
-        <v>1.9956</v>
+        <v>2.0473</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.9956</v>
+        <v>2.0473</v>
       </c>
       <c r="I41" t="n">
-        <v>1.9956</v>
+        <v>2.0473</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.9956</v>
+        <v>2.0473</v>
       </c>
       <c r="N41" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MaSvAl</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.9861</v>
+        <v>1.9956</v>
       </c>
       <c r="C42" t="n">
-        <v>1.3611</v>
+        <v>1.3676</v>
       </c>
       <c r="D42" t="n">
-        <v>0.381</v>
+        <v>0.3511</v>
       </c>
       <c r="E42" t="n">
-        <v>1.9861</v>
+        <v>1.9956</v>
       </c>
       <c r="F42" t="n">
-        <v>1.9861</v>
+        <v>1.9956</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.9861</v>
+        <v>1.9956</v>
       </c>
       <c r="I42" t="n">
-        <v>1.9861</v>
+        <v>1.9956</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>204</v>
+        <v>107</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.9861</v>
+        <v>1.9956</v>
       </c>
       <c r="N42" t="n">
-        <v>204</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>MaSvAl</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.9431</v>
+        <v>1.9861</v>
       </c>
       <c r="C43" t="n">
-        <v>1.3316</v>
+        <v>1.3611</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3636</v>
+        <v>0.3474</v>
       </c>
       <c r="E43" t="n">
-        <v>1.9431</v>
+        <v>1.9861</v>
       </c>
       <c r="F43" t="n">
-        <v>1.9431</v>
+        <v>1.9861</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.9431</v>
+        <v>1.9861</v>
       </c>
       <c r="I43" t="n">
-        <v>1.9431</v>
+        <v>1.9861</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.9431</v>
+        <v>1.9861</v>
       </c>
       <c r="N43" t="n">
-        <v>178</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.9144</v>
+        <v>1.9431</v>
       </c>
       <c r="C44" t="n">
-        <v>1.3119</v>
+        <v>1.3316</v>
       </c>
       <c r="D44" t="n">
-        <v>0.352</v>
+        <v>0.3302</v>
       </c>
       <c r="E44" t="n">
-        <v>1.9144</v>
+        <v>1.9431</v>
       </c>
       <c r="F44" t="n">
-        <v>2.3163</v>
+        <v>1.9431</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.4019</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.3163</v>
+        <v>1.9431</v>
       </c>
       <c r="I44" t="n">
-        <v>2.3271</v>
+        <v>1.9431</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.4019</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="L44" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.9252</v>
+        <v>1.9431</v>
       </c>
       <c r="N44" t="n">
-        <v>232</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.8888</v>
+        <v>1.9087</v>
       </c>
       <c r="C45" t="n">
-        <v>1.2944</v>
+        <v>1.308</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3417</v>
+        <v>0.3165</v>
       </c>
       <c r="E45" t="n">
-        <v>1.8888</v>
+        <v>1.9087</v>
       </c>
       <c r="F45" t="n">
-        <v>1.8888</v>
+        <v>2.3106</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.4019</v>
       </c>
       <c r="H45" t="n">
-        <v>1.8888</v>
+        <v>2.3106</v>
       </c>
       <c r="I45" t="n">
-        <v>1.8888</v>
+        <v>2.3301</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.4019</v>
       </c>
       <c r="K45" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M45" t="n">
-        <v>1.8888</v>
+        <v>1.9282</v>
       </c>
       <c r="N45" t="n">
-        <v>148</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.8805</v>
+        <v>1.8888</v>
       </c>
       <c r="C46" t="n">
-        <v>1.2887</v>
+        <v>1.2944</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3383</v>
+        <v>0.3086</v>
       </c>
       <c r="E46" t="n">
-        <v>1.8805</v>
+        <v>1.8888</v>
       </c>
       <c r="F46" t="n">
-        <v>1.9988</v>
+        <v>1.8888</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.1183</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.9988</v>
+        <v>1.8888</v>
       </c>
       <c r="I46" t="n">
-        <v>1.9988</v>
+        <v>1.8888</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.1183</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L46" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.8805</v>
+        <v>1.8888</v>
       </c>
       <c r="N46" t="n">
-        <v>192</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.8721</v>
+        <v>1.8805</v>
       </c>
       <c r="C47" t="n">
-        <v>1.2829</v>
+        <v>1.2887</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3349</v>
+        <v>0.3053</v>
       </c>
       <c r="E47" t="n">
-        <v>1.8721</v>
+        <v>1.8805</v>
       </c>
       <c r="F47" t="n">
-        <v>1.8721</v>
+        <v>1.9988</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.1183</v>
       </c>
       <c r="H47" t="n">
-        <v>1.8721</v>
+        <v>1.9988</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8721</v>
+        <v>1.9988</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.1183</v>
       </c>
       <c r="K47" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M47" t="n">
-        <v>1.8721</v>
+        <v>1.8805</v>
       </c>
       <c r="N47" t="n">
-        <v>137</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.8688</v>
+        <v>1.8721</v>
       </c>
       <c r="C48" t="n">
-        <v>1.2807</v>
+        <v>1.2829</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3336</v>
+        <v>0.3019</v>
       </c>
       <c r="E48" t="n">
-        <v>1.8688</v>
+        <v>1.8721</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8688</v>
+        <v>1.8721</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.8688</v>
+        <v>1.8721</v>
       </c>
       <c r="I48" t="n">
-        <v>1.8688</v>
+        <v>1.8721</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.8688</v>
+        <v>1.8721</v>
       </c>
       <c r="N48" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.8282</v>
+        <v>1.8688</v>
       </c>
       <c r="C49" t="n">
-        <v>1.2529</v>
+        <v>1.2807</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3172</v>
+        <v>0.3006</v>
       </c>
       <c r="E49" t="n">
-        <v>1.8282</v>
+        <v>1.8688</v>
       </c>
       <c r="F49" t="n">
-        <v>1.8282</v>
+        <v>1.8688</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.8282</v>
+        <v>1.8688</v>
       </c>
       <c r="I49" t="n">
-        <v>1.8282</v>
+        <v>1.8688</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.8282</v>
+        <v>1.8688</v>
       </c>
       <c r="N49" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.7862</v>
+        <v>1.8282</v>
       </c>
       <c r="C50" t="n">
-        <v>1.2241</v>
+        <v>1.2529</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3002</v>
+        <v>0.2844</v>
       </c>
       <c r="E50" t="n">
-        <v>1.7862</v>
+        <v>1.8282</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7862</v>
+        <v>1.8282</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.7862</v>
+        <v>1.8282</v>
       </c>
       <c r="I50" t="n">
-        <v>1.7862</v>
+        <v>1.8282</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.7862</v>
+        <v>1.8282</v>
       </c>
       <c r="N50" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.7856</v>
+        <v>1.7862</v>
       </c>
       <c r="C51" t="n">
-        <v>1.2237</v>
+        <v>1.2241</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3</v>
+        <v>0.2677</v>
       </c>
       <c r="E51" t="n">
-        <v>1.7856</v>
+        <v>1.7862</v>
       </c>
       <c r="F51" t="n">
-        <v>2.7856</v>
+        <v>1.7862</v>
       </c>
       <c r="G51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.7856</v>
+        <v>1.7862</v>
       </c>
       <c r="I51" t="n">
-        <v>2.7856</v>
+        <v>1.7862</v>
       </c>
       <c r="J51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.7856</v>
+        <v>1.7862</v>
       </c>
       <c r="N51" t="n">
-        <v>192</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.709</v>
+        <v>1.7856</v>
       </c>
       <c r="C52" t="n">
-        <v>1.1712</v>
+        <v>1.2237</v>
       </c>
       <c r="D52" t="n">
-        <v>0.269</v>
+        <v>0.2675</v>
       </c>
       <c r="E52" t="n">
-        <v>1.709</v>
+        <v>1.7856</v>
       </c>
       <c r="F52" t="n">
-        <v>1.709</v>
+        <v>2.7856</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>1.709</v>
+        <v>2.7856</v>
       </c>
       <c r="I52" t="n">
-        <v>1.709</v>
+        <v>2.7856</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K52" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M52" t="n">
-        <v>1.709</v>
+        <v>1.7856</v>
       </c>
       <c r="N52" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.6624</v>
+        <v>1.7204</v>
       </c>
       <c r="C53" t="n">
-        <v>1.1392</v>
+        <v>1.179</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2502</v>
+        <v>0.2415</v>
       </c>
       <c r="E53" t="n">
-        <v>1.6624</v>
+        <v>1.7204</v>
       </c>
       <c r="F53" t="n">
-        <v>1.6624</v>
+        <v>1.7204</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.6624</v>
+        <v>1.7204</v>
       </c>
       <c r="I53" t="n">
-        <v>1.6624</v>
+        <v>1.7204</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1.6624</v>
+        <v>1.7204</v>
       </c>
       <c r="N53" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.606</v>
+        <v>1.709</v>
       </c>
       <c r="C54" t="n">
-        <v>1.1006</v>
+        <v>1.1712</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2274</v>
+        <v>0.237</v>
       </c>
       <c r="E54" t="n">
-        <v>1.606</v>
+        <v>1.709</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.5742</v>
+        <v>1.709</v>
       </c>
       <c r="G54" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5742</v>
+        <v>1.709</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5769</v>
+        <v>1.709</v>
       </c>
       <c r="J54" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L54" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1.6033</v>
+        <v>1.709</v>
       </c>
       <c r="N54" t="n">
-        <v>394</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.5375</v>
+        <v>1.6906</v>
       </c>
       <c r="C55" t="n">
-        <v>1.0536</v>
+        <v>1.1586</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1998</v>
+        <v>0.2296</v>
       </c>
       <c r="E55" t="n">
-        <v>1.5375</v>
+        <v>1.6906</v>
       </c>
       <c r="F55" t="n">
-        <v>1.5375</v>
+        <v>1.6906</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.5375</v>
+        <v>1.6906</v>
       </c>
       <c r="I55" t="n">
-        <v>1.5375</v>
+        <v>1.6906</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1.5375</v>
+        <v>1.6906</v>
       </c>
       <c r="N55" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.511</v>
+        <v>1.6081</v>
       </c>
       <c r="C56" t="n">
-        <v>1.0355</v>
+        <v>1.102</v>
       </c>
       <c r="D56" t="n">
-        <v>0.189</v>
+        <v>0.1968</v>
       </c>
       <c r="E56" t="n">
-        <v>1.511</v>
+        <v>1.6081</v>
       </c>
       <c r="F56" t="n">
-        <v>1.511</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="H56" t="n">
-        <v>1.511</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>1.511</v>
+        <v>-0.5769</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="K56" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="M56" t="n">
-        <v>1.511</v>
+        <v>1.6033</v>
       </c>
       <c r="N56" t="n">
-        <v>137</v>
+        <v>394</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.4607</v>
+        <v>1.5965</v>
       </c>
       <c r="C57" t="n">
-        <v>1.001</v>
+        <v>1.0941</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1687</v>
+        <v>0.1921</v>
       </c>
       <c r="E57" t="n">
-        <v>1.4607</v>
+        <v>1.5965</v>
       </c>
       <c r="F57" t="n">
-        <v>1.4607</v>
+        <v>1.5965</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1.4607</v>
+        <v>1.5965</v>
       </c>
       <c r="I57" t="n">
-        <v>1.4607</v>
+        <v>1.5965</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1.4607</v>
+        <v>1.5965</v>
       </c>
       <c r="N57" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.45</v>
+        <v>1.5198</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9937</v>
+        <v>1.0415</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1644</v>
+        <v>0.1616</v>
       </c>
       <c r="E58" t="n">
-        <v>1.45</v>
+        <v>1.5198</v>
       </c>
       <c r="F58" t="n">
-        <v>1.45</v>
+        <v>1.5198</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1.45</v>
+        <v>1.5198</v>
       </c>
       <c r="I58" t="n">
-        <v>1.45</v>
+        <v>1.5198</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.45</v>
+        <v>1.5198</v>
       </c>
       <c r="N58" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.4034</v>
+        <v>1.4607</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9617</v>
+        <v>1.001</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1456</v>
+        <v>0.138</v>
       </c>
       <c r="E59" t="n">
-        <v>1.4034</v>
+        <v>1.4607</v>
       </c>
       <c r="F59" t="n">
-        <v>1.4034</v>
+        <v>1.4607</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.4034</v>
+        <v>1.4607</v>
       </c>
       <c r="I59" t="n">
-        <v>1.4034</v>
+        <v>1.4607</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1.4034</v>
+        <v>1.4607</v>
       </c>
       <c r="N59" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.3823</v>
+        <v>1.45</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9473</v>
+        <v>0.9937</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1371</v>
+        <v>0.1338</v>
       </c>
       <c r="E60" t="n">
-        <v>1.3823</v>
+        <v>1.45</v>
       </c>
       <c r="F60" t="n">
-        <v>1.3823</v>
+        <v>1.45</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.3823</v>
+        <v>1.45</v>
       </c>
       <c r="I60" t="n">
-        <v>1.3823</v>
+        <v>1.45</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1.3823</v>
+        <v>1.45</v>
       </c>
       <c r="N60" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.326</v>
+        <v>1.4034</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9087</v>
+        <v>0.9617</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1143</v>
+        <v>0.1152</v>
       </c>
       <c r="E61" t="n">
-        <v>1.326</v>
+        <v>1.4034</v>
       </c>
       <c r="F61" t="n">
-        <v>1.326</v>
+        <v>1.4034</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.326</v>
+        <v>1.4034</v>
       </c>
       <c r="I61" t="n">
-        <v>1.326</v>
+        <v>1.4034</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1.326</v>
+        <v>1.4034</v>
       </c>
       <c r="N61" t="n">
         <v>92</v>
@@ -3252,829 +3252,829 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.3221</v>
+        <v>1.3823</v>
       </c>
       <c r="C62" t="n">
-        <v>0.906</v>
+        <v>0.9473</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1127</v>
+        <v>0.1068</v>
       </c>
       <c r="E62" t="n">
-        <v>1.3221</v>
+        <v>1.3823</v>
       </c>
       <c r="F62" t="n">
-        <v>1.165</v>
+        <v>1.3823</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1571</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.165</v>
+        <v>1.3823</v>
       </c>
       <c r="I62" t="n">
-        <v>1.165</v>
+        <v>1.3823</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1571</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="L62" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1.3221</v>
+        <v>1.3823</v>
       </c>
       <c r="N62" t="n">
-        <v>376</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.2853</v>
+        <v>1.326</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8808</v>
+        <v>0.9087</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0979</v>
+        <v>0.0844</v>
       </c>
       <c r="E63" t="n">
-        <v>1.2853</v>
+        <v>1.326</v>
       </c>
       <c r="F63" t="n">
-        <v>1.2853</v>
+        <v>1.326</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.2853</v>
+        <v>1.326</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2853</v>
+        <v>1.326</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1.2853</v>
+        <v>1.326</v>
       </c>
       <c r="N63" t="n">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.2806</v>
+        <v>1.3221</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8776</v>
+        <v>0.906</v>
       </c>
       <c r="D64" t="n">
-        <v>0.096</v>
+        <v>0.0828</v>
       </c>
       <c r="E64" t="n">
-        <v>1.2806</v>
+        <v>1.3221</v>
       </c>
       <c r="F64" t="n">
-        <v>1.2806</v>
+        <v>1.165</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.1571</v>
       </c>
       <c r="H64" t="n">
-        <v>1.2806</v>
+        <v>1.165</v>
       </c>
       <c r="I64" t="n">
-        <v>1.2806</v>
+        <v>1.165</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.1571</v>
       </c>
       <c r="K64" t="n">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="M64" t="n">
-        <v>1.2806</v>
+        <v>1.3221</v>
       </c>
       <c r="N64" t="n">
-        <v>204</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.2681</v>
+        <v>1.3181</v>
       </c>
       <c r="C65" t="n">
-        <v>0.869</v>
+        <v>0.9033</v>
       </c>
       <c r="D65" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>1.2681</v>
+        <v>1.3181</v>
       </c>
       <c r="F65" t="n">
-        <v>1.2681</v>
+        <v>1.3181</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.2681</v>
+        <v>1.3181</v>
       </c>
       <c r="I65" t="n">
-        <v>1.2681</v>
+        <v>1.3181</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1.2681</v>
+        <v>1.3181</v>
       </c>
       <c r="N65" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.1847</v>
+        <v>1.2853</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8119</v>
+        <v>0.8808</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0572</v>
+        <v>0.0682</v>
       </c>
       <c r="E66" t="n">
-        <v>1.1847</v>
+        <v>1.2853</v>
       </c>
       <c r="F66" t="n">
-        <v>1.1847</v>
+        <v>1.2853</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.1847</v>
+        <v>1.2853</v>
       </c>
       <c r="I66" t="n">
-        <v>1.1847</v>
+        <v>1.2853</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1.1847</v>
+        <v>1.2853</v>
       </c>
       <c r="N66" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.1647</v>
+        <v>1.2806</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7982</v>
+        <v>0.8776</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0492</v>
+        <v>0.0663</v>
       </c>
       <c r="E67" t="n">
-        <v>1.1647</v>
+        <v>1.2806</v>
       </c>
       <c r="F67" t="n">
-        <v>1.1647</v>
+        <v>1.2806</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1.1647</v>
+        <v>1.2806</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1647</v>
+        <v>1.2806</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1.1647</v>
+        <v>1.2806</v>
       </c>
       <c r="N67" t="n">
-        <v>159</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.1252</v>
+        <v>1.1847</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7711</v>
+        <v>0.8119</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0332</v>
+        <v>0.0281</v>
       </c>
       <c r="E68" t="n">
-        <v>1.1252</v>
+        <v>1.1847</v>
       </c>
       <c r="F68" t="n">
-        <v>1.1252</v>
+        <v>1.1847</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1.1252</v>
+        <v>1.1847</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1252</v>
+        <v>1.1847</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>105</v>
+        <v>180</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1.1252</v>
+        <v>1.1847</v>
       </c>
       <c r="N68" t="n">
-        <v>105</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.0803</v>
+        <v>1.1588</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7403</v>
+        <v>0.7941</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0151</v>
+        <v>0.0178</v>
       </c>
       <c r="E69" t="n">
-        <v>1.0803</v>
+        <v>1.1588</v>
       </c>
       <c r="F69" t="n">
-        <v>1.0803</v>
+        <v>1.1588</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1.0803</v>
+        <v>1.1588</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0803</v>
+        <v>1.1588</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1.0803</v>
+        <v>1.1588</v>
       </c>
       <c r="N69" t="n">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8487</v>
+        <v>1.1252</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5816</v>
+        <v>0.7711</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.0785</v>
+        <v>0.0044</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8487</v>
+        <v>1.1252</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8487</v>
+        <v>1.1252</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8487</v>
+        <v>1.1252</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8487</v>
+        <v>1.1252</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0.8487</v>
+        <v>1.1252</v>
       </c>
       <c r="N70" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8387</v>
+        <v>1.0803</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5748</v>
+        <v>0.7403</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.0825</v>
+        <v>-0.0135</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8387</v>
+        <v>1.0803</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8387</v>
+        <v>1.0803</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8387</v>
+        <v>1.0803</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8387</v>
+        <v>1.0803</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8387</v>
+        <v>1.0803</v>
       </c>
       <c r="N71" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7381</v>
+        <v>0.9987</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5058</v>
+        <v>0.6844</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.1232</v>
+        <v>-0.046</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7381</v>
+        <v>0.9987</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7381</v>
+        <v>0.9987</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.7381</v>
+        <v>0.9987</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7381</v>
+        <v>0.9987</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0.7381</v>
+        <v>0.9987</v>
       </c>
       <c r="N72" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7345</v>
+        <v>0.8387</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5033</v>
+        <v>0.5748</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1246</v>
+        <v>-0.1098</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7345</v>
+        <v>0.8387</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7345</v>
+        <v>0.8387</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.7345</v>
+        <v>0.8387</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7345</v>
+        <v>0.8387</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7345</v>
+        <v>0.8387</v>
       </c>
       <c r="N73" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6832</v>
+        <v>0.7381</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4682</v>
+        <v>0.5058</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1454</v>
+        <v>-0.1499</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6832</v>
+        <v>0.7381</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6832</v>
+        <v>0.7381</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6832</v>
+        <v>0.7381</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6832</v>
+        <v>0.7381</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6832</v>
+        <v>0.7381</v>
       </c>
       <c r="N74" t="n">
-        <v>180</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4528</v>
+        <v>0.5033</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.1544</v>
+        <v>-0.1513</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="N75" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>0.429</v>
+        <v>0.4528</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.1685</v>
+        <v>-0.1806</v>
       </c>
       <c r="E76" t="n">
-        <v>0.626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>0.626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0.626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>64</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5864</v>
+        <v>0.626</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4019</v>
+        <v>0.429</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.1845</v>
+        <v>-0.1945</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5864</v>
+        <v>0.626</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5864</v>
+        <v>0.626</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5864</v>
+        <v>0.626</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5864</v>
+        <v>0.626</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0.5864</v>
+        <v>0.626</v>
       </c>
       <c r="N77" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.551</v>
+        <v>0.5864</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3776</v>
+        <v>0.4019</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.1988</v>
+        <v>-0.2103</v>
       </c>
       <c r="E78" t="n">
-        <v>0.551</v>
+        <v>0.5864</v>
       </c>
       <c r="F78" t="n">
-        <v>0.551</v>
+        <v>0.5864</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.551</v>
+        <v>0.5864</v>
       </c>
       <c r="I78" t="n">
-        <v>0.551</v>
+        <v>0.5864</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0.551</v>
+        <v>0.5864</v>
       </c>
       <c r="N78" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5324</v>
+        <v>0.551</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3649</v>
+        <v>0.3776</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2063</v>
+        <v>-0.2244</v>
       </c>
       <c r="E79" t="n">
-        <v>0.5324</v>
+        <v>0.551</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5324</v>
+        <v>0.551</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.5324</v>
+        <v>0.551</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5324</v>
+        <v>0.551</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0.5324</v>
+        <v>0.551</v>
       </c>
       <c r="N79" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80">
@@ -4090,7 +4090,7 @@
         <v>0.3193</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.2331</v>
+        <v>-0.2583</v>
       </c>
       <c r="E80" t="n">
         <v>0.4659</v>
@@ -4136,7 +4136,7 @@
         <v>0.2978</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.2458</v>
+        <v>-0.2708</v>
       </c>
       <c r="E81" t="n">
         <v>0.4345</v>
@@ -4182,7 +4182,7 @@
         <v>0.2757</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.2588</v>
+        <v>-0.2836</v>
       </c>
       <c r="E82" t="n">
         <v>0.4023</v>
@@ -4218,1565 +4218,1565 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>z4KR</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.287</v>
+        <v>0.2882</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1967</v>
+        <v>0.1975</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.3054</v>
+        <v>-0.3291</v>
       </c>
       <c r="E83" t="n">
-        <v>0.287</v>
+        <v>0.2882</v>
       </c>
       <c r="F83" t="n">
-        <v>0.287</v>
+        <v>0.2882</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.287</v>
+        <v>0.2882</v>
       </c>
       <c r="I83" t="n">
-        <v>0.287</v>
+        <v>0.2882</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0.287</v>
+        <v>0.2882</v>
       </c>
       <c r="N83" t="n">
-        <v>92</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>xeedo</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.243</v>
+        <v>0.287</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1665</v>
+        <v>0.1967</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.3232</v>
+        <v>-0.3296</v>
       </c>
       <c r="E84" t="n">
-        <v>0.243</v>
+        <v>0.287</v>
       </c>
       <c r="F84" t="n">
-        <v>0.243</v>
+        <v>0.287</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.243</v>
+        <v>0.287</v>
       </c>
       <c r="I84" t="n">
-        <v>0.243</v>
+        <v>0.287</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.243</v>
+        <v>0.287</v>
       </c>
       <c r="N84" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>xeedo</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.2417</v>
+        <v>0.243</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1656</v>
+        <v>0.1665</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.3237</v>
+        <v>-0.3471</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2417</v>
+        <v>0.243</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="G85" t="n">
-        <v>0.3098</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3098</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="L85" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2417</v>
+        <v>0.243</v>
       </c>
       <c r="N85" t="n">
-        <v>353</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>slaxejezzz</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.195</v>
+        <v>0.2417</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1336</v>
+        <v>0.1656</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.3426</v>
+        <v>-0.3476</v>
       </c>
       <c r="E86" t="n">
-        <v>0.195</v>
+        <v>0.2417</v>
       </c>
       <c r="F86" t="n">
-        <v>0.195</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>0.3098</v>
       </c>
       <c r="H86" t="n">
-        <v>0.195</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>0.195</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>0.3098</v>
       </c>
       <c r="K86" t="n">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M86" t="n">
-        <v>0.195</v>
+        <v>0.2417</v>
       </c>
       <c r="N86" t="n">
-        <v>100</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>slaxejezzz</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="C87" t="n">
-        <v>0.122</v>
+        <v>0.1336</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.3495</v>
+        <v>-0.3662</v>
       </c>
       <c r="E87" t="n">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="F87" t="n">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="I87" t="n">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="N87" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>venomzera</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.1183</v>
+        <v>0.178</v>
       </c>
       <c r="C88" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.3736</v>
+        <v>-0.373</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1183</v>
+        <v>0.178</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1183</v>
+        <v>0.178</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1183</v>
+        <v>0.178</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1183</v>
+        <v>0.178</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0.1183</v>
+        <v>0.178</v>
       </c>
       <c r="N88" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>clax</t>
+          <t>venomzera</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0936</v>
+        <v>0.1183</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0641</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.3835</v>
+        <v>-0.3968</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0936</v>
+        <v>0.1183</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0936</v>
+        <v>0.1183</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0936</v>
+        <v>0.1183</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0936</v>
+        <v>0.1183</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0.0936</v>
+        <v>0.1183</v>
       </c>
       <c r="N89" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>clax</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0813</v>
+        <v>0.0936</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0557</v>
+        <v>0.0641</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.3885</v>
+        <v>-0.4066</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0813</v>
+        <v>0.0936</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0813</v>
+        <v>0.0936</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0813</v>
+        <v>0.0936</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0813</v>
+        <v>0.0936</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0813</v>
+        <v>0.0936</v>
       </c>
       <c r="N90" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0128</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.4162</v>
+        <v>-0.4071</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0128</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0128</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0128</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0128</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0.0128</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="N91" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>xelex</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.0285</v>
+        <v>0.0819</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.0195</v>
+        <v>0.0561</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.4329</v>
+        <v>-0.4113</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.0285</v>
+        <v>0.0819</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.0285</v>
+        <v>0.2377</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>-0.1558</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.0285</v>
+        <v>0.2377</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0285</v>
+        <v>0.2397</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>-0.1558</v>
       </c>
       <c r="K92" t="n">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.0285</v>
+        <v>0.0839</v>
       </c>
       <c r="N92" t="n">
-        <v>165</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.0664</v>
+        <v>0.0813</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.0455</v>
+        <v>0.0557</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.4482</v>
+        <v>-0.4115</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.0664</v>
+        <v>0.0813</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.0664</v>
+        <v>0.0813</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.0664</v>
+        <v>0.0813</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0664</v>
+        <v>0.0813</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>-0.0664</v>
+        <v>0.0813</v>
       </c>
       <c r="N93" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>qw1nk1</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.1633</v>
+        <v>0.0128</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.1119</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.4873</v>
+        <v>-0.4388</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.1633</v>
+        <v>0.0128</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.1633</v>
+        <v>0.0128</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.1633</v>
+        <v>0.0128</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1633</v>
+        <v>0.0128</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.1633</v>
+        <v>0.0128</v>
       </c>
       <c r="N94" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>qw1nk1</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1633</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1194</v>
+        <v>-0.1119</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.4918</v>
+        <v>-0.509</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1633</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1633</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1633</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1633</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.1743</v>
+        <v>-0.1633</v>
       </c>
       <c r="N95" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.1809</v>
+        <v>-0.1743</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.124</v>
+        <v>-0.1194</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.4944</v>
+        <v>-0.5134</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.1809</v>
+        <v>-0.1743</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.1809</v>
+        <v>-0.1743</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.1809</v>
+        <v>-0.1743</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1809</v>
+        <v>-0.1743</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.1809</v>
+        <v>-0.1743</v>
       </c>
       <c r="N96" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.1843</v>
+        <v>-0.1809</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.1263</v>
+        <v>-0.124</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.4958</v>
+        <v>-0.516</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.1843</v>
+        <v>-0.1809</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.1843</v>
+        <v>-0.1809</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.1843</v>
+        <v>-0.1809</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1843</v>
+        <v>-0.1809</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.1843</v>
+        <v>-0.1809</v>
       </c>
       <c r="N97" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.2042</v>
+        <v>-0.1843</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1399</v>
+        <v>-0.1263</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.5039</v>
+        <v>-0.5173</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.2042</v>
+        <v>-0.1843</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.2042</v>
+        <v>-0.1843</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.2042</v>
+        <v>-0.1843</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2042</v>
+        <v>-0.1843</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.2042</v>
+        <v>-0.1843</v>
       </c>
       <c r="N98" t="n">
-        <v>61</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.2246</v>
+        <v>-0.2042</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.1539</v>
+        <v>-0.1399</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.5121</v>
+        <v>-0.5253</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.2246</v>
+        <v>-0.2042</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.2246</v>
+        <v>-0.2042</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.2246</v>
+        <v>-0.2042</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2246</v>
+        <v>-0.2042</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.2246</v>
+        <v>-0.2042</v>
       </c>
       <c r="N99" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mo0N</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2556</v>
+        <v>-0.2246</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.1752</v>
+        <v>-0.1539</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.5246</v>
+        <v>-0.5334</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.2556</v>
+        <v>-0.2246</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.2556</v>
+        <v>-0.2246</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.2556</v>
+        <v>-0.2246</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2556</v>
+        <v>-0.2246</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>-0.2556</v>
+        <v>-0.2246</v>
       </c>
       <c r="N100" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>mo0N</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.2579</v>
+        <v>-0.2556</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.1767</v>
+        <v>-0.1752</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.5255</v>
+        <v>-0.5457</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.2579</v>
+        <v>-0.2556</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.2579</v>
+        <v>-0.2556</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.2579</v>
+        <v>-0.2556</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2579</v>
+        <v>-0.2556</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>53</v>
+        <v>204</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.2579</v>
+        <v>-0.2556</v>
       </c>
       <c r="N101" t="n">
-        <v>53</v>
+        <v>204</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sFade8</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2579</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.1824</v>
+        <v>-0.1767</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.5289</v>
+        <v>-0.5467</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2579</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2579</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2579</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2579</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2579</v>
       </c>
       <c r="N102" t="n">
-        <v>204</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>sFade8</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.279</v>
+        <v>-0.2662</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.1912</v>
+        <v>-0.1824</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.5341</v>
+        <v>-0.55</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.279</v>
+        <v>-0.2662</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.279</v>
+        <v>-0.2662</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.279</v>
+        <v>-0.2662</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.279</v>
+        <v>-0.2662</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>87</v>
+        <v>204</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>-0.279</v>
+        <v>-0.2662</v>
       </c>
       <c r="N103" t="n">
-        <v>87</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.2808</v>
+        <v>-0.279</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.1924</v>
+        <v>-0.1912</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5551</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.2808</v>
+        <v>-0.279</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.2808</v>
+        <v>-0.279</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.2808</v>
+        <v>-0.279</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2808</v>
+        <v>-0.279</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.2808</v>
+        <v>-0.279</v>
       </c>
       <c r="N104" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AZUWU</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.3008</v>
+        <v>-0.2808</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.2061</v>
+        <v>-0.1924</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.5429</v>
+        <v>-0.5558</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.3008</v>
+        <v>-0.2808</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.3008</v>
+        <v>-0.2808</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.3008</v>
+        <v>-0.2808</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3008</v>
+        <v>-0.2808</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>-0.3008</v>
+        <v>-0.2808</v>
       </c>
       <c r="N105" t="n">
-        <v>66</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>AZUWU</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.3208</v>
+        <v>-0.3008</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.2198</v>
+        <v>-0.2061</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.551</v>
+        <v>-0.5637</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.3208</v>
+        <v>-0.3008</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.3208</v>
+        <v>-0.3008</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.3208</v>
+        <v>-0.3008</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3208</v>
+        <v>-0.3008</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>-0.3208</v>
+        <v>-0.3008</v>
       </c>
       <c r="N106" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bibu</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.3667</v>
+        <v>-0.3208</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.2513</v>
+        <v>-0.2198</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.5695</v>
+        <v>-0.5717</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.3667</v>
+        <v>-0.3208</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.3667</v>
+        <v>-0.3208</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.3667</v>
+        <v>-0.3208</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.3667</v>
+        <v>-0.3208</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.3667</v>
+        <v>-0.3208</v>
       </c>
       <c r="N107" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>Bibu</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.4078</v>
+        <v>-0.3667</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.2795</v>
+        <v>-0.2513</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.5861</v>
+        <v>-0.59</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.4078</v>
+        <v>-0.3667</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.4078</v>
+        <v>-0.3667</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.4078</v>
+        <v>-0.3667</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.4078</v>
+        <v>-0.3667</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.4078</v>
+        <v>-0.3667</v>
       </c>
       <c r="N108" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.4163</v>
+        <v>-0.4078</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2853</v>
+        <v>-0.2795</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.5895</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.4163</v>
+        <v>-0.4078</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.4163</v>
+        <v>-0.4078</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.4163</v>
+        <v>-0.4078</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4163</v>
+        <v>-0.4078</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.4163</v>
+        <v>-0.4078</v>
       </c>
       <c r="N109" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.4258</v>
+        <v>-0.4163</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.2918</v>
+        <v>-0.2853</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.5934</v>
+        <v>-0.6098</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.4258</v>
+        <v>-0.4163</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.4258</v>
+        <v>-0.4163</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.4258</v>
+        <v>-0.4163</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4258</v>
+        <v>-0.4163</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-0.4258</v>
+        <v>-0.4163</v>
       </c>
       <c r="N110" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>tikuak</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.4284</v>
+        <v>-0.4258</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.2936</v>
+        <v>-0.2918</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.5944</v>
+        <v>-0.6135</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.4284</v>
+        <v>-0.4258</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.4284</v>
+        <v>-0.4258</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.4284</v>
+        <v>-0.4258</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4284</v>
+        <v>-0.4258</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-0.4284</v>
+        <v>-0.4258</v>
       </c>
       <c r="N111" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>xelex</t>
+          <t>tikuak</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.482</v>
+        <v>-0.4284</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.3303</v>
+        <v>-0.2936</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.6161</v>
+        <v>-0.6146</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.482</v>
+        <v>-0.4284</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.3262</v>
+        <v>-0.4284</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.1558</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.3262</v>
+        <v>-0.4284</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.3277</v>
+        <v>-0.4284</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.1558</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="L112" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>-0.4835</v>
+        <v>-0.4284</v>
       </c>
       <c r="N112" t="n">
-        <v>268</v>
+        <v>159</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>sinnopsyy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.5171</v>
+        <v>-0.4751</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.3544</v>
+        <v>-0.3256</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.6303</v>
+        <v>-0.6332</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.5171</v>
+        <v>-0.4751</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.5171</v>
+        <v>-0.4751</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.5171</v>
+        <v>-0.4751</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5171</v>
+        <v>-0.4751</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-0.5171</v>
+        <v>-0.4751</v>
       </c>
       <c r="N113" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.5313</v>
+        <v>-0.5171</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.3641</v>
+        <v>-0.3544</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.636</v>
+        <v>-0.6499</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.5313</v>
+        <v>-0.5171</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.5313</v>
+        <v>-0.5171</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.5313</v>
+        <v>-0.5171</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5313</v>
+        <v>-0.5171</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.5313</v>
+        <v>-0.5171</v>
       </c>
       <c r="N114" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.536</v>
+        <v>-0.5313</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.3673</v>
+        <v>-0.3641</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.6379</v>
+        <v>-0.6556</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.536</v>
+        <v>-0.5313</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.536</v>
+        <v>-0.5313</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.536</v>
+        <v>-0.5313</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.536</v>
+        <v>-0.5313</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.536</v>
+        <v>-0.5313</v>
       </c>
       <c r="N115" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sinnopsyy</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.5658</v>
+        <v>-0.536</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.3877</v>
+        <v>-0.3673</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.6499</v>
+        <v>-0.6575</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.5658</v>
+        <v>-0.536</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.5658</v>
+        <v>-0.536</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.5658</v>
+        <v>-0.536</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5658</v>
+        <v>-0.536</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.5658</v>
+        <v>-0.536</v>
       </c>
       <c r="N116" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
     </row>
     <row r="117">
@@ -5792,7 +5792,7 @@
         <v>-0.3889</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.6506</v>
+        <v>-0.67</v>
       </c>
       <c r="E117" t="n">
         <v>-0.5675</v>
@@ -5838,7 +5838,7 @@
         <v>-0.4278</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.6735</v>
+        <v>-0.6926</v>
       </c>
       <c r="E118" t="n">
         <v>-0.6242</v>
@@ -5884,7 +5884,7 @@
         <v>-0.4383</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.6797</v>
+        <v>-0.6987</v>
       </c>
       <c r="E119" t="n">
         <v>-0.6395999999999999</v>
@@ -5930,7 +5930,7 @@
         <v>-0.4424</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.6822</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="E120" t="n">
         <v>-0.6456</v>
@@ -5976,7 +5976,7 @@
         <v>-0.4468</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.6848</v>
+        <v>-0.7037</v>
       </c>
       <c r="E121" t="n">
         <v>-0.652</v>
@@ -6022,7 +6022,7 @@
         <v>-0.4855</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.7076</v>
+        <v>-0.7262</v>
       </c>
       <c r="E122" t="n">
         <v>-0.7085</v>
@@ -6068,7 +6068,7 @@
         <v>-0.5154</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.7252</v>
+        <v>-0.7435</v>
       </c>
       <c r="E123" t="n">
         <v>-0.7521</v>
@@ -6114,7 +6114,7 @@
         <v>-0.5182</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.7268</v>
+        <v>-0.7451</v>
       </c>
       <c r="E124" t="n">
         <v>-0.7561</v>
@@ -6150,1151 +6150,1151 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.7972</v>
+        <v>-0.777</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.5463</v>
+        <v>-0.5325</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.7972</v>
+        <v>-0.777</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.7972</v>
+        <v>-0.777</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.7972</v>
+        <v>-0.777</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7972</v>
+        <v>-0.777</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.7972</v>
+        <v>-0.777</v>
       </c>
       <c r="N125" t="n">
-        <v>61</v>
+        <v>148</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>X5G7V</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.883</v>
+        <v>-0.7972</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.6051</v>
+        <v>-0.5463</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.7781</v>
+        <v>-0.7615</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.883</v>
+        <v>-0.7972</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.883</v>
+        <v>-0.7972</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.883</v>
+        <v>-0.7972</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.883</v>
+        <v>-0.7972</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.883</v>
+        <v>-0.7972</v>
       </c>
       <c r="N126" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>mhL</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.8888</v>
+        <v>-0.8003</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.6091</v>
+        <v>-0.5484</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.7804</v>
+        <v>-0.7628</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.8888</v>
+        <v>-0.8003</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.8888</v>
+        <v>0.1997</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.8888</v>
+        <v>0.1997</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.8888</v>
+        <v>0.2013</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K127" t="n">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.8888</v>
+        <v>-0.7987</v>
       </c>
       <c r="N127" t="n">
-        <v>87</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>d1Ledez</t>
+          <t>X5G7V</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.9272</v>
+        <v>-0.883</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.6354</v>
+        <v>-0.6051</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.7957</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.9272</v>
+        <v>-0.883</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.9272</v>
+        <v>-0.883</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.9272</v>
+        <v>-0.883</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.9272</v>
+        <v>-0.883</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.9272</v>
+        <v>-0.883</v>
       </c>
       <c r="N128" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>mhL</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.9596</v>
+        <v>-0.8888</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.6576</v>
+        <v>-0.6091</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.798</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.9596</v>
+        <v>-0.8888</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.9596</v>
+        <v>-0.8888</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.9596</v>
+        <v>-0.8888</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.9596</v>
+        <v>-0.8888</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.9596</v>
+        <v>-0.8888</v>
       </c>
       <c r="N129" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>d1Ledez</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.9775</v>
+        <v>-0.9272</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6354</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.8163</v>
+        <v>-0.8133</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.9775</v>
+        <v>-0.9272</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.9775</v>
+        <v>-0.9272</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-0.9775</v>
+        <v>-0.9272</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.9775</v>
+        <v>-0.9272</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.9775</v>
+        <v>-0.9272</v>
       </c>
       <c r="N130" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-1.0399</v>
+        <v>-0.9275</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.7126</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.8415</v>
+        <v>-0.8134</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.0399</v>
+        <v>-0.9275</v>
       </c>
       <c r="F131" t="n">
-        <v>-1.0399</v>
+        <v>-0.9275</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>-1.0399</v>
+        <v>-0.9275</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.0399</v>
+        <v>-0.9275</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>-1.0399</v>
+        <v>-0.9275</v>
       </c>
       <c r="N131" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>n0te</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-1.0756</v>
+        <v>-0.9596</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.7371</v>
+        <v>-0.6576</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.8559</v>
+        <v>-0.8262</v>
       </c>
       <c r="E132" t="n">
-        <v>-1.0756</v>
+        <v>-0.9596</v>
       </c>
       <c r="F132" t="n">
-        <v>-1.0756</v>
+        <v>-0.9596</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-1.0756</v>
+        <v>-0.9596</v>
       </c>
       <c r="I132" t="n">
-        <v>-1.0756</v>
+        <v>-0.9596</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>-1.0756</v>
+        <v>-0.9596</v>
       </c>
       <c r="N132" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>m1N1</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-1.1317</v>
+        <v>-1.0399</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.7755</v>
+        <v>-0.7126</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-0.8582</v>
       </c>
       <c r="E133" t="n">
-        <v>-1.1317</v>
+        <v>-1.0399</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.1317</v>
+        <v>-1.0399</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-1.1317</v>
+        <v>-1.0399</v>
       </c>
       <c r="I133" t="n">
-        <v>-1.1317</v>
+        <v>-1.0399</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-1.1317</v>
+        <v>-1.0399</v>
       </c>
       <c r="N133" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>n0te</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-1.136</v>
+        <v>-1.0756</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.7785</v>
+        <v>-0.7371</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.8803</v>
+        <v>-0.8724</v>
       </c>
       <c r="E134" t="n">
-        <v>-1.136</v>
+        <v>-1.0756</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.136</v>
+        <v>-1.0756</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-1.136</v>
+        <v>-1.0756</v>
       </c>
       <c r="I134" t="n">
-        <v>-1.136</v>
+        <v>-1.0756</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>-1.136</v>
+        <v>-1.0756</v>
       </c>
       <c r="N134" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>m1N1</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-1.1437</v>
+        <v>-1.1317</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.7755</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.8834</v>
+        <v>-0.8948</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.1437</v>
+        <v>-1.1317</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.1437</v>
+        <v>-1.1317</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-1.1437</v>
+        <v>-1.1317</v>
       </c>
       <c r="I135" t="n">
-        <v>-1.1437</v>
+        <v>-1.1317</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>-1.1437</v>
+        <v>-1.1317</v>
       </c>
       <c r="N135" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-1.1973</v>
+        <v>-1.136</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.8205</v>
+        <v>-0.7785</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.905</v>
+        <v>-0.8965</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.1973</v>
+        <v>-1.136</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.1973</v>
+        <v>-1.136</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.1973</v>
+        <v>-1.136</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1973</v>
+        <v>-1.136</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-1.1973</v>
+        <v>-1.136</v>
       </c>
       <c r="N136" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-1.198</v>
+        <v>-1.1973</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.821</v>
+        <v>-0.8205</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.9053</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>-1.198</v>
+        <v>-1.1973</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.198</v>
+        <v>-1.1973</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.198</v>
+        <v>-1.1973</v>
       </c>
       <c r="I137" t="n">
-        <v>-1.198</v>
+        <v>-1.1973</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-1.198</v>
+        <v>-1.1973</v>
       </c>
       <c r="N137" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>poiii</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-1.206</v>
+        <v>-1.198</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.8265</v>
+        <v>-0.821</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.9086</v>
+        <v>-0.9212</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.206</v>
+        <v>-1.198</v>
       </c>
       <c r="F138" t="n">
-        <v>-1.206</v>
+        <v>-1.198</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-1.206</v>
+        <v>-1.198</v>
       </c>
       <c r="I138" t="n">
-        <v>-1.206</v>
+        <v>-1.198</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>-1.206</v>
+        <v>-1.198</v>
       </c>
       <c r="N138" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>gr1ks</t>
+          <t>poiii</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-1.2182</v>
+        <v>-1.206</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.8348</v>
+        <v>-0.8265</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.9135</v>
+        <v>-0.9244</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.2182</v>
+        <v>-1.206</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.2182</v>
+        <v>-1.206</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>-1.2182</v>
+        <v>-1.206</v>
       </c>
       <c r="I139" t="n">
-        <v>-1.2182</v>
+        <v>-1.206</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-1.2182</v>
+        <v>-1.206</v>
       </c>
       <c r="N139" t="n">
-        <v>148</v>
+        <v>53</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>gr1ks</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-1.2808</v>
+        <v>-1.2182</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.8777</v>
+        <v>-0.8348</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.9388</v>
+        <v>-0.9292</v>
       </c>
       <c r="E140" t="n">
-        <v>-1.2808</v>
+        <v>-1.2182</v>
       </c>
       <c r="F140" t="n">
-        <v>-1.2808</v>
+        <v>-1.2182</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.2808</v>
+        <v>-1.2182</v>
       </c>
       <c r="I140" t="n">
-        <v>-1.2808</v>
+        <v>-1.2182</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>-1.2808</v>
+        <v>-1.2182</v>
       </c>
       <c r="N140" t="n">
-        <v>61</v>
+        <v>148</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-1.2833</v>
+        <v>-1.2808</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.8794</v>
+        <v>-0.8777</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.9398</v>
+        <v>-0.9542</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.2833</v>
+        <v>-1.2808</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.1579</v>
+        <v>-1.2808</v>
       </c>
       <c r="G141" t="n">
-        <v>-1.1254</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.1579</v>
+        <v>-1.2808</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1586</v>
+        <v>-1.2808</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.1254</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="L141" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-1.284</v>
+        <v>-1.2808</v>
       </c>
       <c r="N141" t="n">
-        <v>394</v>
+        <v>61</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kashl1d</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.3106</v>
+        <v>-1.2827</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.8981</v>
+        <v>-0.879</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.9508</v>
+        <v>-0.9549</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.3106</v>
+        <v>-1.2827</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.3106</v>
+        <v>-0.1573</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>-1.1254</v>
       </c>
       <c r="H142" t="n">
-        <v>-1.3106</v>
+        <v>-0.1573</v>
       </c>
       <c r="I142" t="n">
-        <v>-1.3106</v>
+        <v>-0.1586</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>-1.1254</v>
       </c>
       <c r="K142" t="n">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="M142" t="n">
-        <v>-1.3106</v>
+        <v>-1.284</v>
       </c>
       <c r="N142" t="n">
-        <v>60</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>nEMANHA</t>
+          <t>kashl1d</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-1.3156</v>
+        <v>-1.3106</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.9016</v>
+        <v>-0.8981</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.9528</v>
+        <v>-0.9661</v>
       </c>
       <c r="E143" t="n">
-        <v>-1.3156</v>
+        <v>-1.3106</v>
       </c>
       <c r="F143" t="n">
-        <v>-1.3156</v>
+        <v>-1.3106</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>-1.3156</v>
+        <v>-1.3106</v>
       </c>
       <c r="I143" t="n">
-        <v>-1.3156</v>
+        <v>-1.3106</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>-1.3156</v>
+        <v>-1.3106</v>
       </c>
       <c r="N143" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>nEMANHA</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-1.3722</v>
+        <v>-1.3156</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.9404</v>
+        <v>-0.9016</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.9757</v>
+        <v>-0.968</v>
       </c>
       <c r="E144" t="n">
-        <v>-1.3722</v>
+        <v>-1.3156</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.3722</v>
+        <v>-1.3156</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.3722</v>
+        <v>-1.3156</v>
       </c>
       <c r="I144" t="n">
-        <v>-1.3722</v>
+        <v>-1.3156</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>-1.3722</v>
+        <v>-1.3156</v>
       </c>
       <c r="N144" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-1.4007</v>
+        <v>-1.3722</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.9599</v>
+        <v>-0.9404</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.9872</v>
+        <v>-0.9906</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.4007</v>
+        <v>-1.3722</v>
       </c>
       <c r="F145" t="n">
-        <v>-1.4007</v>
+        <v>-1.3722</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>-1.4007</v>
+        <v>-1.3722</v>
       </c>
       <c r="I145" t="n">
-        <v>-1.4007</v>
+        <v>-1.3722</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>-1.4007</v>
+        <v>-1.3722</v>
       </c>
       <c r="N145" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sirah</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-1.4701</v>
+        <v>-1.4007</v>
       </c>
       <c r="C146" t="n">
-        <v>-1.0075</v>
+        <v>-0.9599</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.0153</v>
+        <v>-1.0019</v>
       </c>
       <c r="E146" t="n">
-        <v>-1.4701</v>
+        <v>-1.4007</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.4701</v>
+        <v>-1.4007</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>-1.4701</v>
+        <v>-1.4007</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.4701</v>
+        <v>-1.4007</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>-1.4701</v>
+        <v>-1.4007</v>
       </c>
       <c r="N146" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>sirah</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-1.5722</v>
+        <v>-1.4701</v>
       </c>
       <c r="C147" t="n">
-        <v>-1.0774</v>
+        <v>-1.0075</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.0565</v>
+        <v>-1.0296</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.5722</v>
+        <v>-1.4701</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.5722</v>
+        <v>-1.4701</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>-1.5722</v>
+        <v>-1.4701</v>
       </c>
       <c r="I147" t="n">
-        <v>-1.5722</v>
+        <v>-1.4701</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>-1.5722</v>
+        <v>-1.4701</v>
       </c>
       <c r="N147" t="n">
-        <v>178</v>
+        <v>53</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-1.6456</v>
+        <v>-1.5722</v>
       </c>
       <c r="C148" t="n">
-        <v>-1.1277</v>
+        <v>-1.0774</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.0861</v>
+        <v>-1.0703</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.6456</v>
+        <v>-1.5722</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.6456</v>
+        <v>-1.5722</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>-1.6456</v>
+        <v>-1.5722</v>
       </c>
       <c r="I148" t="n">
-        <v>-1.6456</v>
+        <v>-1.5722</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.6456</v>
+        <v>-1.5722</v>
       </c>
       <c r="N148" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-1.7087</v>
+        <v>-1.6456</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.171</v>
+        <v>-1.1277</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.1116</v>
+        <v>-1.0995</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.7087</v>
+        <v>-1.6456</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.7087</v>
+        <v>-1.6456</v>
       </c>
       <c r="G149" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.7087</v>
+        <v>-1.6456</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.712</v>
+        <v>-1.6456</v>
       </c>
       <c r="J149" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L149" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>-1.712</v>
+        <v>-1.6456</v>
       </c>
       <c r="N149" t="n">
-        <v>232</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150">
@@ -7310,7 +7310,7 @@
         <v>-1.1854</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.1202</v>
+        <v>-1.1331</v>
       </c>
       <c r="E150" t="n">
         <v>-1.7298</v>
@@ -7356,7 +7356,7 @@
         <v>-1.2185</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.1396</v>
+        <v>-1.1523</v>
       </c>
       <c r="E151" t="n">
         <v>-1.778</v>
@@ -7402,7 +7402,7 @@
         <v>-1.2267</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.1445</v>
+        <v>-1.157</v>
       </c>
       <c r="E152" t="n">
         <v>-1.79</v>
@@ -7448,7 +7448,7 @@
         <v>-1.2646</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.1669</v>
+        <v>-1.1791</v>
       </c>
       <c r="E153" t="n">
         <v>-1.8454</v>
@@ -7494,7 +7494,7 @@
         <v>-1.3303</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.2056</v>
+        <v>-1.2173</v>
       </c>
       <c r="E154" t="n">
         <v>-1.9412</v>
@@ -7540,7 +7540,7 @@
         <v>-1.3756</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.2323</v>
+        <v>-1.2436</v>
       </c>
       <c r="E155" t="n">
         <v>-2.0073</v>
@@ -7586,7 +7586,7 @@
         <v>-1.4495</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.2759</v>
+        <v>-1.2866</v>
       </c>
       <c r="E156" t="n">
         <v>-2.1152</v>
@@ -7632,7 +7632,7 @@
         <v>-1.4779</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.2926</v>
+        <v>-1.3031</v>
       </c>
       <c r="E157" t="n">
         <v>-2.1566</v>
@@ -7678,7 +7678,7 @@
         <v>-1.5325</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.3248</v>
+        <v>-1.3349</v>
       </c>
       <c r="E158" t="n">
         <v>-2.2363</v>
@@ -7718,25 +7718,25 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-2.621</v>
+        <v>-2.6149</v>
       </c>
       <c r="C159" t="n">
-        <v>-1.7962</v>
+        <v>-1.792</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.4802</v>
+        <v>-1.4857</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.621</v>
+        <v>-2.6149</v>
       </c>
       <c r="F159" t="n">
-        <v>-1.621</v>
+        <v>-1.6149</v>
       </c>
       <c r="G159" t="n">
         <v>-1</v>
       </c>
       <c r="H159" t="n">
-        <v>-1.621</v>
+        <v>-1.6149</v>
       </c>
       <c r="I159" t="n">
         <v>-1.6285</v>
@@ -7770,7 +7770,7 @@
         <v>-1.9035</v>
       </c>
       <c r="D160" t="n">
-        <v>-1.5435</v>
+        <v>-1.5505</v>
       </c>
       <c r="E160" t="n">
         <v>-2.7777</v>
@@ -7816,7 +7816,7 @@
         <v>-2.8719</v>
       </c>
       <c r="D161" t="n">
-        <v>-2.1144</v>
+        <v>-2.1135</v>
       </c>
       <c r="E161" t="n">
         <v>-4.1908</v>

--- a/database/event/8261/event_8261_evp_summary.xlsx
+++ b/database/event/8261/event_8261_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.4241</v>
+        <v>11.9552</v>
       </c>
       <c r="C2" t="n">
-        <v>7.8289</v>
+        <v>8.1928</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5763</v>
+        <v>4.7263</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4241</v>
+        <v>11.9552</v>
       </c>
       <c r="F2" t="n">
         <v>5.2334</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8325</v>
+        <v>6.8031</v>
       </c>
       <c r="C3" t="n">
-        <v>4.6823</v>
+        <v>4.6621</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4861</v>
+        <v>2.425</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8325</v>
+        <v>6.8031</v>
       </c>
       <c r="F3" t="n">
         <v>2.9061</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2776</v>
+        <v>6.5027</v>
       </c>
       <c r="C4" t="n">
-        <v>4.302</v>
+        <v>4.4563</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2335</v>
+        <v>2.2908</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2776</v>
+        <v>6.5027</v>
       </c>
       <c r="F4" t="n">
         <v>3.3199</v>
@@ -630,139 +630,139 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9676</v>
+        <v>6.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4.0896</v>
+        <v>4.1803</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0924</v>
+        <v>2.1109</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9676</v>
+        <v>6.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6082</v>
+        <v>3.5707</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3594</v>
+        <v>2.3003</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9836</v>
+        <v>5.0902</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9836</v>
+        <v>5.0902</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3594</v>
+        <v>2.3003</v>
       </c>
       <c r="K5" t="n">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="L5" t="n">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="M5" t="n">
-        <v>6.343</v>
+        <v>7.3905</v>
       </c>
       <c r="N5" t="n">
-        <v>376</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.871</v>
+        <v>6.0928</v>
       </c>
       <c r="C6" t="n">
-        <v>4.0234</v>
+        <v>4.1754</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0484</v>
+        <v>2.1077</v>
       </c>
       <c r="E6" t="n">
-        <v>5.871</v>
+        <v>6.0928</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5707</v>
+        <v>4.2824</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3003</v>
+        <v>1.3511</v>
       </c>
       <c r="H6" t="n">
-        <v>5.0902</v>
+        <v>6.6479</v>
       </c>
       <c r="I6" t="n">
-        <v>5.0902</v>
+        <v>6.6479</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3003</v>
+        <v>1.3511</v>
       </c>
       <c r="K6" t="n">
-        <v>232</v>
+        <v>101</v>
       </c>
       <c r="L6" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>7.3905</v>
+        <v>7.999</v>
       </c>
       <c r="N6" t="n">
-        <v>353</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6335</v>
+        <v>5.9815</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8606</v>
+        <v>4.0991</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9403</v>
+        <v>2.058</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6335</v>
+        <v>5.9815</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2824</v>
+        <v>2.6082</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3511</v>
+        <v>3.3594</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6479</v>
+        <v>2.9836</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6479</v>
+        <v>2.9836</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3511</v>
+        <v>3.3594</v>
       </c>
       <c r="K7" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="M7" t="n">
-        <v>7.999</v>
+        <v>6.343</v>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4275</v>
+        <v>5.6349</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7194</v>
+        <v>3.8616</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8465</v>
+        <v>1.9032</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4275</v>
+        <v>5.6349</v>
       </c>
       <c r="F8" t="n">
         <v>3.092</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.2393</v>
+        <v>5.3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5905</v>
+        <v>3.6321</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7608</v>
+        <v>1.7536</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2393</v>
+        <v>5.3</v>
       </c>
       <c r="F9" t="n">
         <v>2.4612</v>
@@ -860,921 +860,921 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.882</v>
+        <v>5.0215</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3456</v>
+        <v>3.4412</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5982</v>
+        <v>1.6292</v>
       </c>
       <c r="E10" t="n">
-        <v>4.882</v>
+        <v>5.0215</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5971</v>
+        <v>4.5325</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2849</v>
+        <v>0.201</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9593</v>
+        <v>7.1953</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9593</v>
+        <v>7.3807</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2849</v>
+        <v>0.201</v>
       </c>
       <c r="K10" t="n">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="L10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="M10" t="n">
-        <v>5.244199999999999</v>
+        <v>7.5817</v>
       </c>
       <c r="N10" t="n">
-        <v>291</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.7335</v>
+        <v>4.9878</v>
       </c>
       <c r="C11" t="n">
-        <v>3.2438</v>
+        <v>3.4181</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5306</v>
+        <v>1.6141</v>
       </c>
       <c r="E11" t="n">
-        <v>4.7335</v>
+        <v>4.9878</v>
       </c>
       <c r="F11" t="n">
-        <v>4.5325</v>
+        <v>2.5971</v>
       </c>
       <c r="G11" t="n">
-        <v>0.201</v>
+        <v>2.2849</v>
       </c>
       <c r="H11" t="n">
-        <v>7.1953</v>
+        <v>2.9593</v>
       </c>
       <c r="I11" t="n">
-        <v>7.3807</v>
+        <v>2.9593</v>
       </c>
       <c r="J11" t="n">
-        <v>0.201</v>
+        <v>2.2849</v>
       </c>
       <c r="K11" t="n">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>7.5817</v>
+        <v>5.244199999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>232</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>tenzy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.0063</v>
+        <v>4.195</v>
       </c>
       <c r="C12" t="n">
-        <v>2.7455</v>
+        <v>2.8748</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1995</v>
+        <v>1.26</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0063</v>
+        <v>4.195</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2279</v>
+        <v>3.6655</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7784</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.34</v>
+        <v>5.2978</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4518</v>
+        <v>5.2978</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7784</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="L12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2302</v>
+        <v>5.2978</v>
       </c>
       <c r="N12" t="n">
-        <v>232</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8153</v>
+        <v>4.0723</v>
       </c>
       <c r="C13" t="n">
-        <v>2.6146</v>
+        <v>2.7907</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1126</v>
+        <v>1.2052</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8153</v>
+        <v>4.0723</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6379</v>
+        <v>3.2279</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1774</v>
+        <v>0.7784</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2372</v>
+        <v>4.34</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2372</v>
+        <v>4.4518</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1774</v>
+        <v>0.7784</v>
       </c>
       <c r="K13" t="n">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="L13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4146</v>
+        <v>5.2302</v>
       </c>
       <c r="N13" t="n">
-        <v>291</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.7763</v>
+        <v>3.9795</v>
       </c>
       <c r="C14" t="n">
-        <v>2.5879</v>
+        <v>2.7271</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0948</v>
+        <v>1.1637</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7763</v>
+        <v>3.9795</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3129</v>
+        <v>3.6379</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4634</v>
+        <v>0.1774</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3373</v>
+        <v>5.2372</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3373</v>
+        <v>5.2372</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4634</v>
+        <v>0.1774</v>
       </c>
       <c r="K14" t="n">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="L14" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8007</v>
+        <v>5.4146</v>
       </c>
       <c r="N14" t="n">
-        <v>353</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tenzy</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.6655</v>
+        <v>3.84</v>
       </c>
       <c r="C15" t="n">
-        <v>2.5119</v>
+        <v>2.6315</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0444</v>
+        <v>1.1014</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6655</v>
+        <v>3.84</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6655</v>
+        <v>3.3876</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2978</v>
+        <v>4.6894</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2978</v>
+        <v>4.6894</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.2978</v>
+        <v>4.6894</v>
       </c>
       <c r="N15" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5977</v>
+        <v>3.5889</v>
       </c>
       <c r="C16" t="n">
-        <v>2.4655</v>
+        <v>2.4595</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0135</v>
+        <v>0.9893</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5977</v>
+        <v>3.5889</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3381</v>
+        <v>2.9457</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2596</v>
+        <v>0.5065</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5811</v>
+        <v>3.7223</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5811</v>
+        <v>3.8182</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2596</v>
+        <v>0.5065</v>
       </c>
       <c r="K16" t="n">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="L16" t="n">
-        <v>219</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8407</v>
+        <v>4.3247</v>
       </c>
       <c r="N16" t="n">
-        <v>376</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4522</v>
+        <v>3.5782</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3658</v>
+        <v>2.4521</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9473</v>
+        <v>0.9845</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4522</v>
+        <v>3.5782</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9457</v>
+        <v>2.3129</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5065</v>
+        <v>1.4634</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7223</v>
+        <v>2.3373</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8182</v>
+        <v>2.3373</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5065</v>
+        <v>1.4634</v>
       </c>
       <c r="K17" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L17" t="n">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3247</v>
+        <v>3.8007</v>
       </c>
       <c r="N17" t="n">
-        <v>268</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3876</v>
+        <v>3.5601</v>
       </c>
       <c r="C18" t="n">
-        <v>2.3215</v>
+        <v>2.4397</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9179</v>
+        <v>0.9764</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3876</v>
+        <v>3.5601</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3876</v>
+        <v>3.3381</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.2596</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6894</v>
+        <v>4.5811</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6894</v>
+        <v>4.5811</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.2596</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6894</v>
+        <v>4.8407</v>
       </c>
       <c r="N18" t="n">
-        <v>117</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.2778</v>
+        <v>3.4544</v>
       </c>
       <c r="C19" t="n">
-        <v>2.2463</v>
+        <v>2.3673</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8679</v>
+        <v>0.9292</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2778</v>
+        <v>3.4544</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3665</v>
+        <v>3.2325</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6443</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3665</v>
+        <v>4.3499</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3759</v>
+        <v>4.3499</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6443</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L19" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2684</v>
+        <v>4.3499</v>
       </c>
       <c r="N19" t="n">
-        <v>394</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.2325</v>
+        <v>3.1545</v>
       </c>
       <c r="C20" t="n">
-        <v>2.2152</v>
+        <v>2.1618</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.7952</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2325</v>
+        <v>3.1545</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2325</v>
+        <v>2.7845</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.2147</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3499</v>
+        <v>3.3695</v>
       </c>
       <c r="I20" t="n">
-        <v>4.3499</v>
+        <v>3.4563</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.2147</v>
       </c>
       <c r="K20" t="n">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3499</v>
+        <v>3.671</v>
       </c>
       <c r="N20" t="n">
-        <v>178</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.059</v>
+        <v>3.126</v>
       </c>
       <c r="C21" t="n">
-        <v>2.0963</v>
+        <v>2.1422</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7683</v>
+        <v>0.7825</v>
       </c>
       <c r="E21" t="n">
-        <v>3.059</v>
+        <v>3.126</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6164</v>
+        <v>-0.3665</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4426</v>
+        <v>3.6443</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0016</v>
+        <v>-0.3665</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0789</v>
+        <v>-0.3759</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4426</v>
+        <v>3.6443</v>
       </c>
       <c r="K21" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L21" t="n">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5215</v>
+        <v>3.2684</v>
       </c>
       <c r="N21" t="n">
-        <v>232</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.0455</v>
+        <v>3.0801</v>
       </c>
       <c r="C22" t="n">
-        <v>2.0871</v>
+        <v>2.1108</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7622</v>
+        <v>0.762</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0455</v>
+        <v>3.0801</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4276</v>
+        <v>3.5114</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4731</v>
+        <v>-0.658</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4276</v>
+        <v>4.9605</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4276</v>
+        <v>4.9605</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4731</v>
+        <v>-0.658</v>
       </c>
       <c r="K22" t="n">
-        <v>232</v>
+        <v>101</v>
       </c>
       <c r="L22" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.0455</v>
+        <v>4.302499999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>353</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9992</v>
+        <v>3.0795</v>
       </c>
       <c r="C23" t="n">
-        <v>2.0553</v>
+        <v>2.1104</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7411</v>
+        <v>0.7617</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9992</v>
+        <v>3.0795</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7845</v>
+        <v>2.7629</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2147</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3695</v>
+        <v>3.3221</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4563</v>
+        <v>3.3221</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2147</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>221</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.671</v>
+        <v>3.3221</v>
       </c>
       <c r="N23" t="n">
-        <v>268</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.975</v>
+        <v>3.0644</v>
       </c>
       <c r="C24" t="n">
-        <v>2.0387</v>
+        <v>2.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7301</v>
+        <v>0.755</v>
       </c>
       <c r="E24" t="n">
-        <v>2.975</v>
+        <v>3.0644</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8504</v>
+        <v>2.8751</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1246</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5137</v>
+        <v>3.5677</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5137</v>
+        <v>3.5677</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1246</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="L24" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6383</v>
+        <v>3.5677</v>
       </c>
       <c r="N24" t="n">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.8751</v>
+        <v>3.0569</v>
       </c>
       <c r="C25" t="n">
-        <v>1.9703</v>
+        <v>2.0949</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6846</v>
+        <v>0.7516</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8751</v>
+        <v>3.0569</v>
       </c>
       <c r="F25" t="n">
-        <v>2.8751</v>
+        <v>2.8118</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5677</v>
+        <v>3.4292</v>
       </c>
       <c r="I25" t="n">
-        <v>3.5677</v>
+        <v>3.4292</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5677</v>
+        <v>3.4292</v>
       </c>
       <c r="N25" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.8534</v>
+        <v>3.0405</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9554</v>
+        <v>2.0836</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6747</v>
+        <v>0.7443</v>
       </c>
       <c r="E26" t="n">
-        <v>2.8534</v>
+        <v>3.0405</v>
       </c>
       <c r="F26" t="n">
-        <v>3.5114</v>
+        <v>2.6164</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.658</v>
+        <v>0.4426</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9605</v>
+        <v>3.0016</v>
       </c>
       <c r="I26" t="n">
-        <v>4.9605</v>
+        <v>3.0789</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.658</v>
+        <v>0.4426</v>
       </c>
       <c r="K26" t="n">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L26" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="M26" t="n">
-        <v>4.302499999999999</v>
+        <v>3.5215</v>
       </c>
       <c r="N26" t="n">
-        <v>144</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.8126</v>
+        <v>3.0387</v>
       </c>
       <c r="C27" t="n">
-        <v>1.9275</v>
+        <v>2.0824</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6562</v>
+        <v>0.7435</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8126</v>
+        <v>3.0387</v>
       </c>
       <c r="F27" t="n">
-        <v>3.4165</v>
+        <v>2.5174</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6039</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7528</v>
+        <v>2.7849</v>
       </c>
       <c r="I27" t="n">
-        <v>4.7528</v>
+        <v>2.7849</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.6039</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="L27" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.148899999999999</v>
+        <v>2.7849</v>
       </c>
       <c r="N27" t="n">
-        <v>291</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8118</v>
+        <v>3.0324</v>
       </c>
       <c r="C28" t="n">
-        <v>1.9269</v>
+        <v>2.0781</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6558</v>
+        <v>0.7407</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8118</v>
+        <v>3.0324</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8118</v>
+        <v>2.7233</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4292</v>
+        <v>3.2355</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4292</v>
+        <v>3.2355</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4292</v>
+        <v>3.2355</v>
       </c>
       <c r="N28" t="n">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.7629</v>
+        <v>3.0262</v>
       </c>
       <c r="C29" t="n">
-        <v>1.8934</v>
+        <v>2.0738</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6335</v>
+        <v>0.7379</v>
       </c>
       <c r="E29" t="n">
-        <v>2.7629</v>
+        <v>3.0262</v>
       </c>
       <c r="F29" t="n">
-        <v>2.7629</v>
+        <v>-0.4276</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3.4731</v>
       </c>
       <c r="H29" t="n">
-        <v>3.3221</v>
+        <v>-0.4276</v>
       </c>
       <c r="I29" t="n">
-        <v>3.3221</v>
+        <v>-0.4276</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3.4731</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3221</v>
+        <v>3.0455</v>
       </c>
       <c r="N29" t="n">
-        <v>100</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.7249</v>
+        <v>2.9465</v>
       </c>
       <c r="C30" t="n">
-        <v>1.8674</v>
+        <v>2.0192</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6162</v>
+        <v>0.7023</v>
       </c>
       <c r="E30" t="n">
-        <v>2.7249</v>
+        <v>2.9465</v>
       </c>
       <c r="F30" t="n">
         <v>2.7249</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.7233</v>
+        <v>2.875</v>
       </c>
       <c r="C31" t="n">
-        <v>1.8663</v>
+        <v>1.9702</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6155</v>
+        <v>0.6704</v>
       </c>
       <c r="E31" t="n">
-        <v>2.7233</v>
+        <v>2.875</v>
       </c>
       <c r="F31" t="n">
-        <v>2.7233</v>
+        <v>2.8504</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1246</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2355</v>
+        <v>3.5137</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2355</v>
+        <v>3.5137</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1246</v>
       </c>
       <c r="K31" t="n">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2355</v>
+        <v>3.6383</v>
       </c>
       <c r="N31" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.6715</v>
+        <v>2.8673</v>
       </c>
       <c r="C32" t="n">
-        <v>1.8308</v>
+        <v>1.9649</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5919</v>
+        <v>0.6669</v>
       </c>
       <c r="E32" t="n">
-        <v>2.6715</v>
+        <v>2.8673</v>
       </c>
       <c r="F32" t="n">
-        <v>2.6715</v>
+        <v>3.4165</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.6039</v>
       </c>
       <c r="H32" t="n">
-        <v>3.1222</v>
+        <v>4.7528</v>
       </c>
       <c r="I32" t="n">
-        <v>3.1222</v>
+        <v>4.7528</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.6039</v>
       </c>
       <c r="K32" t="n">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1222</v>
+        <v>4.148899999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>178</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.6304</v>
+        <v>2.8582</v>
       </c>
       <c r="C33" t="n">
-        <v>1.8026</v>
+        <v>1.9587</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5732</v>
+        <v>0.6629</v>
       </c>
       <c r="E33" t="n">
-        <v>2.6304</v>
+        <v>2.8582</v>
       </c>
       <c r="F33" t="n">
         <v>2.6304</v>
@@ -1964,323 +1964,323 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.613</v>
+        <v>2.8202</v>
       </c>
       <c r="C34" t="n">
-        <v>1.7907</v>
+        <v>1.9327</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5653</v>
+        <v>0.6459</v>
       </c>
       <c r="E34" t="n">
-        <v>2.613</v>
+        <v>2.8202</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6998</v>
+        <v>2.4927</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9132</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.6998</v>
+        <v>2.7308</v>
       </c>
       <c r="I34" t="n">
-        <v>1.6998</v>
+        <v>2.7308</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9132</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="L34" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.613</v>
+        <v>2.7308</v>
       </c>
       <c r="N34" t="n">
-        <v>376</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.5594</v>
+        <v>2.7959</v>
       </c>
       <c r="C35" t="n">
-        <v>1.7539</v>
+        <v>1.916</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5409</v>
+        <v>0.635</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5594</v>
+        <v>2.7959</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5594</v>
+        <v>2.6715</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.8769</v>
+        <v>3.1222</v>
       </c>
       <c r="I35" t="n">
-        <v>2.8769</v>
+        <v>3.1222</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.8769</v>
+        <v>3.1222</v>
       </c>
       <c r="N35" t="n">
-        <v>142</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.5563</v>
+        <v>2.6573</v>
       </c>
       <c r="C36" t="n">
-        <v>1.7518</v>
+        <v>1.821</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5395</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>2.5563</v>
+        <v>2.6573</v>
       </c>
       <c r="F36" t="n">
-        <v>2.5563</v>
+        <v>2.5388</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.8701</v>
+        <v>2.8317</v>
       </c>
       <c r="I36" t="n">
-        <v>2.8701</v>
+        <v>2.8317</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.8701</v>
+        <v>2.8317</v>
       </c>
       <c r="N36" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.5388</v>
+        <v>2.6545</v>
       </c>
       <c r="C37" t="n">
-        <v>1.7398</v>
+        <v>1.8191</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5315</v>
+        <v>0.5719</v>
       </c>
       <c r="E37" t="n">
-        <v>2.5388</v>
+        <v>2.6545</v>
       </c>
       <c r="F37" t="n">
-        <v>2.5388</v>
+        <v>2.5563</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.8317</v>
+        <v>2.8701</v>
       </c>
       <c r="I37" t="n">
-        <v>2.8317</v>
+        <v>2.8701</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.8317</v>
+        <v>2.8701</v>
       </c>
       <c r="N37" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.5174</v>
+        <v>2.5861</v>
       </c>
       <c r="C38" t="n">
-        <v>1.7252</v>
+        <v>1.7722</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5218</v>
+        <v>0.5413</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5174</v>
+        <v>2.5861</v>
       </c>
       <c r="F38" t="n">
-        <v>2.5174</v>
+        <v>1.6998</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.9132</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7849</v>
+        <v>1.6998</v>
       </c>
       <c r="I38" t="n">
-        <v>2.7849</v>
+        <v>1.6998</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.9132</v>
       </c>
       <c r="K38" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7849</v>
+        <v>2.613</v>
       </c>
       <c r="N38" t="n">
-        <v>159</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.4927</v>
+        <v>2.5753</v>
       </c>
       <c r="C39" t="n">
-        <v>1.7082</v>
+        <v>1.7648</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5105</v>
+        <v>0.5365</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4927</v>
+        <v>2.5753</v>
       </c>
       <c r="F39" t="n">
-        <v>2.4927</v>
+        <v>2.5594</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.7308</v>
+        <v>2.8769</v>
       </c>
       <c r="I39" t="n">
-        <v>2.7308</v>
+        <v>2.8769</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.7308</v>
+        <v>2.8769</v>
       </c>
       <c r="N39" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.4496</v>
+        <v>2.5717</v>
       </c>
       <c r="C40" t="n">
-        <v>1.6787</v>
+        <v>1.7624</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4909</v>
+        <v>0.5349</v>
       </c>
       <c r="E40" t="n">
-        <v>2.4496</v>
+        <v>2.5717</v>
       </c>
       <c r="F40" t="n">
-        <v>2.9984</v>
+        <v>2.2499</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5488</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3.8376</v>
+        <v>2.2499</v>
       </c>
       <c r="I40" t="n">
-        <v>3.8376</v>
+        <v>2.2499</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5488</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="L40" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2888</v>
+        <v>2.2499</v>
       </c>
       <c r="N40" t="n">
-        <v>192</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.421</v>
+        <v>2.499</v>
       </c>
       <c r="C41" t="n">
-        <v>1.6591</v>
+        <v>1.7125</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4779</v>
+        <v>0.5024</v>
       </c>
       <c r="E41" t="n">
-        <v>2.421</v>
+        <v>2.499</v>
       </c>
       <c r="F41" t="n">
         <v>2.7078</v>
@@ -2332,139 +2332,139 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.3762</v>
+        <v>2.4891</v>
       </c>
       <c r="C42" t="n">
-        <v>1.6284</v>
+        <v>1.7058</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4575</v>
+        <v>0.498</v>
       </c>
       <c r="E42" t="n">
-        <v>2.3762</v>
+        <v>2.4891</v>
       </c>
       <c r="F42" t="n">
-        <v>2.8376</v>
+        <v>2.3279</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.4614</v>
+        <v>-0.0435</v>
       </c>
       <c r="H42" t="n">
-        <v>3.4856</v>
+        <v>2.3701</v>
       </c>
       <c r="I42" t="n">
-        <v>3.4856</v>
+        <v>2.3701</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4614</v>
+        <v>-0.0435</v>
       </c>
       <c r="K42" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M42" t="n">
-        <v>3.0242</v>
+        <v>2.3266</v>
       </c>
       <c r="N42" t="n">
-        <v>144</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.3299</v>
+        <v>2.4621</v>
       </c>
       <c r="C43" t="n">
-        <v>1.5967</v>
+        <v>1.6873</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4364</v>
+        <v>0.4859</v>
       </c>
       <c r="E43" t="n">
-        <v>2.3299</v>
+        <v>2.4621</v>
       </c>
       <c r="F43" t="n">
-        <v>3.1187</v>
+        <v>2.8376</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.4614</v>
       </c>
       <c r="H43" t="n">
-        <v>4.1009</v>
+        <v>3.4856</v>
       </c>
       <c r="I43" t="n">
-        <v>4.1009</v>
+        <v>3.4856</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.4614</v>
       </c>
       <c r="K43" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3121</v>
+        <v>3.0242</v>
       </c>
       <c r="N43" t="n">
-        <v>192</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.3105</v>
+        <v>2.4226</v>
       </c>
       <c r="C44" t="n">
-        <v>1.5834</v>
+        <v>1.6602</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4276</v>
+        <v>0.4683</v>
       </c>
       <c r="E44" t="n">
-        <v>2.3105</v>
+        <v>2.4226</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5681</v>
+        <v>2.9984</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2576</v>
+        <v>-0.5488</v>
       </c>
       <c r="H44" t="n">
-        <v>2.8959</v>
+        <v>3.8376</v>
       </c>
       <c r="I44" t="n">
-        <v>2.9705</v>
+        <v>3.8376</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.2576</v>
+        <v>-0.5488</v>
       </c>
       <c r="K44" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="L44" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M44" t="n">
-        <v>2.7129</v>
+        <v>3.2888</v>
       </c>
       <c r="N44" t="n">
-        <v>232</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.3054</v>
+        <v>2.4194</v>
       </c>
       <c r="C45" t="n">
-        <v>1.5799</v>
+        <v>1.658</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4253</v>
+        <v>0.4669</v>
       </c>
       <c r="E45" t="n">
-        <v>2.3054</v>
+        <v>2.4194</v>
       </c>
       <c r="F45" t="n">
         <v>2.3054</v>
@@ -2516,47 +2516,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.3043</v>
+        <v>2.4189</v>
       </c>
       <c r="C46" t="n">
-        <v>1.5791</v>
+        <v>1.6577</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4248</v>
+        <v>0.4666</v>
       </c>
       <c r="E46" t="n">
-        <v>2.3043</v>
+        <v>2.4189</v>
       </c>
       <c r="F46" t="n">
-        <v>2.3043</v>
+        <v>3.1187</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>2.3184</v>
+        <v>4.1009</v>
       </c>
       <c r="I46" t="n">
-        <v>2.3184</v>
+        <v>4.1009</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M46" t="n">
-        <v>2.3184</v>
+        <v>3.3121</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47">
@@ -2566,16 +2566,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.2967</v>
+        <v>2.3935</v>
       </c>
       <c r="C47" t="n">
-        <v>1.5739</v>
+        <v>1.6403</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4213</v>
+        <v>0.4553</v>
       </c>
       <c r="E47" t="n">
-        <v>2.2967</v>
+        <v>2.3935</v>
       </c>
       <c r="F47" t="n">
         <v>2.2967</v>
@@ -2608,170 +2608,170 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.2844</v>
+        <v>2.3739</v>
       </c>
       <c r="C48" t="n">
-        <v>1.5655</v>
+        <v>1.6268</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4157</v>
+        <v>0.4465</v>
       </c>
       <c r="E48" t="n">
-        <v>2.2844</v>
+        <v>2.3739</v>
       </c>
       <c r="F48" t="n">
-        <v>2.3279</v>
+        <v>2.5681</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0435</v>
+        <v>-0.2576</v>
       </c>
       <c r="H48" t="n">
-        <v>2.3701</v>
+        <v>2.8959</v>
       </c>
       <c r="I48" t="n">
-        <v>2.3701</v>
+        <v>2.9705</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.0435</v>
+        <v>-0.2576</v>
       </c>
       <c r="K48" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="L48" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="M48" t="n">
-        <v>2.3266</v>
+        <v>2.7129</v>
       </c>
       <c r="N48" t="n">
-        <v>192</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>JBOEN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.2785</v>
+        <v>2.3531</v>
       </c>
       <c r="C49" t="n">
-        <v>1.5614</v>
+        <v>1.6126</v>
       </c>
       <c r="D49" t="n">
-        <v>0.413</v>
+        <v>0.4373</v>
       </c>
       <c r="E49" t="n">
-        <v>2.2785</v>
+        <v>2.3531</v>
       </c>
       <c r="F49" t="n">
-        <v>2.2785</v>
+        <v>2.0945</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.2785</v>
+        <v>2.0945</v>
       </c>
       <c r="I49" t="n">
-        <v>2.2785</v>
+        <v>2.0945</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>204</v>
+        <v>107</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.2785</v>
+        <v>2.0945</v>
       </c>
       <c r="N49" t="n">
-        <v>204</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.2694</v>
+        <v>2.352</v>
       </c>
       <c r="C50" t="n">
-        <v>1.5552</v>
+        <v>1.6118</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4089</v>
+        <v>0.4368</v>
       </c>
       <c r="E50" t="n">
-        <v>2.2694</v>
+        <v>2.352</v>
       </c>
       <c r="F50" t="n">
-        <v>0.094</v>
+        <v>2.2174</v>
       </c>
       <c r="G50" t="n">
-        <v>2.1754</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.094</v>
+        <v>2.2174</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0964</v>
+        <v>2.2174</v>
       </c>
       <c r="J50" t="n">
-        <v>2.1754</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="L50" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.2718</v>
+        <v>2.2174</v>
       </c>
       <c r="N50" t="n">
-        <v>394</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MaSvAl</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.2673</v>
+        <v>2.344</v>
       </c>
       <c r="C51" t="n">
-        <v>1.5538</v>
+        <v>1.6063</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4079</v>
+        <v>0.4332</v>
       </c>
       <c r="E51" t="n">
-        <v>2.2673</v>
+        <v>2.344</v>
       </c>
       <c r="F51" t="n">
-        <v>2.2673</v>
+        <v>2.2785</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.2673</v>
+        <v>2.2785</v>
       </c>
       <c r="I51" t="n">
-        <v>2.2673</v>
+        <v>2.2785</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.2673</v>
+        <v>2.2785</v>
       </c>
       <c r="N51" t="n">
         <v>204</v>
@@ -2792,185 +2792,185 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.2499</v>
+        <v>2.3332</v>
       </c>
       <c r="C52" t="n">
-        <v>1.5418</v>
+        <v>1.5989</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4</v>
+        <v>0.4284</v>
       </c>
       <c r="E52" t="n">
-        <v>2.2499</v>
+        <v>2.3332</v>
       </c>
       <c r="F52" t="n">
-        <v>2.2499</v>
+        <v>2.113</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.2499</v>
+        <v>2.113</v>
       </c>
       <c r="I52" t="n">
-        <v>2.2499</v>
+        <v>2.113</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.2499</v>
+        <v>2.113</v>
       </c>
       <c r="N52" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.2174</v>
+        <v>2.2706</v>
       </c>
       <c r="C53" t="n">
-        <v>1.5196</v>
+        <v>1.556</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3852</v>
+        <v>0.4004</v>
       </c>
       <c r="E53" t="n">
-        <v>2.2174</v>
+        <v>2.2706</v>
       </c>
       <c r="F53" t="n">
-        <v>2.2174</v>
+        <v>0.094</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2.1754</v>
       </c>
       <c r="H53" t="n">
-        <v>2.2174</v>
+        <v>0.094</v>
       </c>
       <c r="I53" t="n">
-        <v>2.2174</v>
+        <v>0.0964</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>2.1754</v>
       </c>
       <c r="K53" t="n">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="M53" t="n">
-        <v>2.2174</v>
+        <v>2.2718</v>
       </c>
       <c r="N53" t="n">
-        <v>107</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.113</v>
+        <v>2.2494</v>
       </c>
       <c r="C54" t="n">
-        <v>1.448</v>
+        <v>1.5415</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3377</v>
+        <v>0.3909</v>
       </c>
       <c r="E54" t="n">
-        <v>2.113</v>
+        <v>2.2494</v>
       </c>
       <c r="F54" t="n">
-        <v>2.113</v>
+        <v>2.0118</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2.113</v>
+        <v>2.0118</v>
       </c>
       <c r="I54" t="n">
-        <v>2.113</v>
+        <v>2.0118</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.113</v>
+        <v>2.0118</v>
       </c>
       <c r="N54" t="n">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.0983</v>
+        <v>2.2377</v>
       </c>
       <c r="C55" t="n">
-        <v>1.438</v>
+        <v>1.5335</v>
       </c>
       <c r="D55" t="n">
-        <v>0.331</v>
+        <v>0.3857</v>
       </c>
       <c r="E55" t="n">
-        <v>2.0983</v>
+        <v>2.2377</v>
       </c>
       <c r="F55" t="n">
-        <v>2.0983</v>
+        <v>2.3043</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2.0983</v>
+        <v>2.3184</v>
       </c>
       <c r="I55" t="n">
-        <v>2.0983</v>
+        <v>2.3184</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.0983</v>
+        <v>2.3184</v>
       </c>
       <c r="N55" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56">
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.0956</v>
+        <v>2.165</v>
       </c>
       <c r="C56" t="n">
-        <v>1.4361</v>
+        <v>1.4837</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3298</v>
+        <v>0.3532</v>
       </c>
       <c r="E56" t="n">
-        <v>2.0956</v>
+        <v>2.165</v>
       </c>
       <c r="F56" t="n">
         <v>2.0956</v>
@@ -3022,185 +3022,185 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JBOEN</t>
+          <t>MaSvAl</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.0945</v>
+        <v>2.1015</v>
       </c>
       <c r="C57" t="n">
-        <v>1.4353</v>
+        <v>1.4401</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3293</v>
+        <v>0.3249</v>
       </c>
       <c r="E57" t="n">
-        <v>2.0945</v>
+        <v>2.1015</v>
       </c>
       <c r="F57" t="n">
-        <v>2.0945</v>
+        <v>2.2673</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2.0945</v>
+        <v>2.2673</v>
       </c>
       <c r="I57" t="n">
-        <v>2.0945</v>
+        <v>2.2673</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2.0945</v>
+        <v>2.2673</v>
       </c>
       <c r="N57" t="n">
-        <v>107</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.0674</v>
+        <v>2.1012</v>
       </c>
       <c r="C58" t="n">
-        <v>1.4168</v>
+        <v>1.4399</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3169</v>
+        <v>0.3247</v>
       </c>
       <c r="E58" t="n">
-        <v>2.0674</v>
+        <v>2.1012</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0674</v>
+        <v>1.9323</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.0674</v>
+        <v>1.9323</v>
       </c>
       <c r="I58" t="n">
-        <v>2.0674</v>
+        <v>1.9323</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.0674</v>
+        <v>1.9323</v>
       </c>
       <c r="N58" t="n">
-        <v>137</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.0565</v>
+        <v>2.0959</v>
       </c>
       <c r="C59" t="n">
-        <v>1.4093</v>
+        <v>1.4363</v>
       </c>
       <c r="D59" t="n">
-        <v>0.312</v>
+        <v>0.3224</v>
       </c>
       <c r="E59" t="n">
-        <v>2.0565</v>
+        <v>2.0959</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0565</v>
+        <v>2.0983</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2.0565</v>
+        <v>2.0983</v>
       </c>
       <c r="I59" t="n">
-        <v>2.0565</v>
+        <v>2.0983</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.0565</v>
+        <v>2.0983</v>
       </c>
       <c r="N59" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.0118</v>
+        <v>2.0874</v>
       </c>
       <c r="C60" t="n">
-        <v>1.3787</v>
+        <v>1.4305</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2916</v>
+        <v>0.3186</v>
       </c>
       <c r="E60" t="n">
-        <v>2.0118</v>
+        <v>2.0874</v>
       </c>
       <c r="F60" t="n">
-        <v>2.0118</v>
+        <v>2.0674</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2.0118</v>
+        <v>2.0674</v>
       </c>
       <c r="I60" t="n">
-        <v>2.0118</v>
+        <v>2.0674</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.0118</v>
+        <v>2.0674</v>
       </c>
       <c r="N60" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61">
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.9823</v>
+        <v>2.0153</v>
       </c>
       <c r="C61" t="n">
-        <v>1.3585</v>
+        <v>1.3811</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2782</v>
+        <v>0.2864</v>
       </c>
       <c r="E61" t="n">
-        <v>1.9823</v>
+        <v>2.0153</v>
       </c>
       <c r="F61" t="n">
         <v>1.9823</v>
@@ -3252,47 +3252,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.9595</v>
+        <v>1.9499</v>
       </c>
       <c r="C62" t="n">
-        <v>1.3428</v>
+        <v>1.3363</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2678</v>
+        <v>0.2572</v>
       </c>
       <c r="E62" t="n">
-        <v>1.9595</v>
+        <v>1.9499</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9595</v>
+        <v>2.0565</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.9595</v>
+        <v>2.0565</v>
       </c>
       <c r="I62" t="n">
-        <v>1.9595</v>
+        <v>2.0565</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1.9595</v>
+        <v>2.0565</v>
       </c>
       <c r="N62" t="n">
-        <v>165</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63">
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.9569</v>
+        <v>1.9467</v>
       </c>
       <c r="C63" t="n">
-        <v>1.3411</v>
+        <v>1.3341</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2666</v>
+        <v>0.2557</v>
       </c>
       <c r="E63" t="n">
-        <v>1.9569</v>
+        <v>1.9467</v>
       </c>
       <c r="F63" t="n">
         <v>1.5744</v>
@@ -3344,139 +3344,139 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.9323</v>
+        <v>1.8844</v>
       </c>
       <c r="C64" t="n">
-        <v>1.3242</v>
+        <v>1.2914</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2554</v>
+        <v>0.2279</v>
       </c>
       <c r="E64" t="n">
-        <v>1.9323</v>
+        <v>1.8844</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9323</v>
+        <v>1.8529</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.9323</v>
+        <v>1.8529</v>
       </c>
       <c r="I64" t="n">
-        <v>1.9323</v>
+        <v>1.8529</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1.9323</v>
+        <v>1.8529</v>
       </c>
       <c r="N64" t="n">
-        <v>92</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.8529</v>
+        <v>1.8687</v>
       </c>
       <c r="C65" t="n">
-        <v>1.2698</v>
+        <v>1.2806</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2193</v>
+        <v>0.2209</v>
       </c>
       <c r="E65" t="n">
-        <v>1.8529</v>
+        <v>1.8687</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8529</v>
+        <v>1.9595</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.8529</v>
+        <v>1.9595</v>
       </c>
       <c r="I65" t="n">
-        <v>1.8529</v>
+        <v>1.9595</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1.8529</v>
+        <v>1.9595</v>
       </c>
       <c r="N65" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.7512</v>
+        <v>1.7917</v>
       </c>
       <c r="C66" t="n">
-        <v>1.2001</v>
+        <v>1.2278</v>
       </c>
       <c r="D66" t="n">
-        <v>0.173</v>
+        <v>0.1865</v>
       </c>
       <c r="E66" t="n">
-        <v>1.7512</v>
+        <v>1.7917</v>
       </c>
       <c r="F66" t="n">
-        <v>1.7512</v>
+        <v>1.4915</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.7512</v>
+        <v>1.4915</v>
       </c>
       <c r="I66" t="n">
-        <v>1.7512</v>
+        <v>1.4915</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1.7512</v>
+        <v>1.4915</v>
       </c>
       <c r="N66" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.6825</v>
+        <v>1.7506</v>
       </c>
       <c r="C67" t="n">
-        <v>1.153</v>
+        <v>1.1997</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1417</v>
+        <v>0.1681</v>
       </c>
       <c r="E67" t="n">
-        <v>1.6825</v>
+        <v>1.7506</v>
       </c>
       <c r="F67" t="n">
         <v>1.6825</v>
@@ -3528,32 +3528,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.5846</v>
+        <v>1.705</v>
       </c>
       <c r="C68" t="n">
-        <v>1.0859</v>
+        <v>1.1684</v>
       </c>
       <c r="D68" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1478</v>
       </c>
       <c r="E68" t="n">
-        <v>1.5846</v>
+        <v>1.705</v>
       </c>
       <c r="F68" t="n">
-        <v>1.5846</v>
+        <v>1.7512</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1.5846</v>
+        <v>1.7512</v>
       </c>
       <c r="I68" t="n">
-        <v>1.5846</v>
+        <v>1.7512</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1.5846</v>
+        <v>1.7512</v>
       </c>
       <c r="N68" t="n">
         <v>180</v>
@@ -3578,16 +3578,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.4915</v>
+        <v>1.5567</v>
       </c>
       <c r="C69" t="n">
-        <v>1.0221</v>
+        <v>1.0668</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0548</v>
+        <v>0.0815</v>
       </c>
       <c r="E69" t="n">
-        <v>1.4915</v>
+        <v>1.5567</v>
       </c>
       <c r="F69" t="n">
         <v>1.4915</v>
@@ -3620,32 +3620,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.4915</v>
+        <v>1.5551</v>
       </c>
       <c r="C70" t="n">
-        <v>1.0221</v>
+        <v>1.0657</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0548</v>
+        <v>0.0808</v>
       </c>
       <c r="E70" t="n">
-        <v>1.4915</v>
+        <v>1.5551</v>
       </c>
       <c r="F70" t="n">
-        <v>1.4915</v>
+        <v>1.4423</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1.4915</v>
+        <v>1.4423</v>
       </c>
       <c r="I70" t="n">
-        <v>1.4915</v>
+        <v>1.4423</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1.4915</v>
+        <v>1.4423</v>
       </c>
       <c r="N70" t="n">
         <v>137</v>
@@ -3666,262 +3666,262 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.4423</v>
+        <v>1.4438</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0324</v>
+        <v>0.0311</v>
       </c>
       <c r="E71" t="n">
-        <v>1.4423</v>
+        <v>1.4438</v>
       </c>
       <c r="F71" t="n">
-        <v>1.4423</v>
+        <v>1.4109</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.4423</v>
+        <v>1.4109</v>
       </c>
       <c r="I71" t="n">
-        <v>1.4423</v>
+        <v>1.4109</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1.4423</v>
+        <v>1.4109</v>
       </c>
       <c r="N71" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.4109</v>
+        <v>1.4307</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9669</v>
+        <v>0.9804</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0181</v>
+        <v>0.0252</v>
       </c>
       <c r="E72" t="n">
-        <v>1.4109</v>
+        <v>1.4307</v>
       </c>
       <c r="F72" t="n">
-        <v>1.4109</v>
+        <v>1.2696</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1.4109</v>
+        <v>1.2696</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4109</v>
+        <v>1.2696</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1.4109</v>
+        <v>1.2696</v>
       </c>
       <c r="N72" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.2696</v>
+        <v>1.4089</v>
       </c>
       <c r="C73" t="n">
-        <v>0.87</v>
+        <v>0.9655</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0463</v>
+        <v>0.0155</v>
       </c>
       <c r="E73" t="n">
-        <v>1.2696</v>
+        <v>1.4089</v>
       </c>
       <c r="F73" t="n">
-        <v>1.2696</v>
+        <v>1.5846</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.2696</v>
+        <v>1.5846</v>
       </c>
       <c r="I73" t="n">
-        <v>1.2696</v>
+        <v>1.5846</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1.2696</v>
+        <v>1.5846</v>
       </c>
       <c r="N73" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.2604</v>
+        <v>1.2958</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8637</v>
+        <v>0.888</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0504</v>
+        <v>-0.035</v>
       </c>
       <c r="E74" t="n">
-        <v>1.2604</v>
+        <v>1.2958</v>
       </c>
       <c r="F74" t="n">
-        <v>0.413</v>
+        <v>1.2385</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8474</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.413</v>
+        <v>1.2385</v>
       </c>
       <c r="I74" t="n">
-        <v>0.413</v>
+        <v>1.2385</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8474</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>232</v>
+        <v>120</v>
       </c>
       <c r="L74" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1.2604</v>
+        <v>1.2385</v>
       </c>
       <c r="N74" t="n">
-        <v>353</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.2598</v>
+        <v>1.2748</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8633</v>
+        <v>0.8736</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0507</v>
+        <v>-0.0444</v>
       </c>
       <c r="E75" t="n">
-        <v>1.2598</v>
+        <v>1.2748</v>
       </c>
       <c r="F75" t="n">
-        <v>1.2598</v>
+        <v>1.1317</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1.2598</v>
+        <v>1.1317</v>
       </c>
       <c r="I75" t="n">
-        <v>1.2598</v>
+        <v>1.1317</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>1.2598</v>
+        <v>1.1317</v>
       </c>
       <c r="N75" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.2385</v>
+        <v>1.2136</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8487</v>
+        <v>0.8317</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0604</v>
+        <v>-0.0717</v>
       </c>
       <c r="E76" t="n">
-        <v>1.2385</v>
+        <v>1.2136</v>
       </c>
       <c r="F76" t="n">
-        <v>1.2385</v>
+        <v>1.2598</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1.2385</v>
+        <v>1.2598</v>
       </c>
       <c r="I76" t="n">
-        <v>1.2385</v>
+        <v>1.2598</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1.2385</v>
+        <v>1.2598</v>
       </c>
       <c r="N76" t="n">
         <v>120</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.1317</v>
+        <v>1.1606</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7755</v>
+        <v>0.7954</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.109</v>
+        <v>-0.0954</v>
       </c>
       <c r="E77" t="n">
-        <v>1.1317</v>
+        <v>1.1606</v>
       </c>
       <c r="F77" t="n">
-        <v>1.1317</v>
+        <v>0.413</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.8474</v>
       </c>
       <c r="H77" t="n">
-        <v>1.1317</v>
+        <v>0.413</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1317</v>
+        <v>0.413</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>0.8474</v>
       </c>
       <c r="K77" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M77" t="n">
-        <v>1.1317</v>
+        <v>1.2604</v>
       </c>
       <c r="N77" t="n">
-        <v>117</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.9215</v>
+        <v>1.0891</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6315</v>
+        <v>0.7464</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.2047</v>
+        <v>-0.1273</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9215</v>
+        <v>1.0891</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9215</v>
+        <v>0.8586</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9215</v>
+        <v>0.8586</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9215</v>
+        <v>0.8586</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0.9215</v>
+        <v>0.8586</v>
       </c>
       <c r="N78" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.903</v>
+        <v>1.0211</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6188</v>
+        <v>0.6998</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2131</v>
+        <v>-0.1577</v>
       </c>
       <c r="E79" t="n">
-        <v>0.903</v>
+        <v>1.0211</v>
       </c>
       <c r="F79" t="n">
         <v>0.903</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.895</v>
+        <v>0.8139</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6133</v>
+        <v>0.5578</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.2168</v>
+        <v>-0.2503</v>
       </c>
       <c r="E80" t="n">
-        <v>0.895</v>
+        <v>0.8139</v>
       </c>
       <c r="F80" t="n">
         <v>0.895</v>
@@ -4126,32 +4126,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8586</v>
+        <v>0.8067</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5884</v>
+        <v>0.5528</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.2334</v>
+        <v>-0.2535</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8586</v>
+        <v>0.8067</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8586</v>
+        <v>0.7295</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8586</v>
+        <v>0.7295</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8586</v>
+        <v>0.7295</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8586</v>
+        <v>0.7295</v>
       </c>
       <c r="N81" t="n">
         <v>61</v>
@@ -4172,599 +4172,599 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8335</v>
+        <v>0.796</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5712</v>
+        <v>0.5455</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.2448</v>
+        <v>-0.2583</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8335</v>
+        <v>0.796</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8335</v>
+        <v>0.9215</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8335</v>
+        <v>0.9215</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8335</v>
+        <v>0.9215</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0.8335</v>
+        <v>0.9215</v>
       </c>
       <c r="N82" t="n">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8139</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5578</v>
+        <v>0.4846</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.2537</v>
+        <v>-0.2979</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8139</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8139</v>
+        <v>0.8335</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8139</v>
+        <v>0.8335</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8139</v>
+        <v>0.8335</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8139</v>
+        <v>0.8335</v>
       </c>
       <c r="N83" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7295</v>
+        <v>0.6751</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4999</v>
+        <v>0.4626</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.2921</v>
+        <v>-0.3123</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7295</v>
+        <v>0.6751</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7295</v>
+        <v>0.8139</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.7295</v>
+        <v>0.8139</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7295</v>
+        <v>0.8139</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.7295</v>
+        <v>0.8139</v>
       </c>
       <c r="N84" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>z4KR</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6721</v>
+        <v>0.5397</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4606</v>
+        <v>0.3699</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.3182</v>
+        <v>-0.3727</v>
       </c>
       <c r="E85" t="n">
-        <v>0.6721</v>
+        <v>0.5397</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6721</v>
+        <v>0.3927</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.6721</v>
+        <v>0.3927</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6721</v>
+        <v>0.3927</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.6721</v>
+        <v>0.3927</v>
       </c>
       <c r="N85" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>venomzera</t>
+          <t>xelex</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5876</v>
+        <v>0.5296</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4027</v>
+        <v>0.3629</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.3567</v>
+        <v>-0.3773</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5876</v>
+        <v>0.5296</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5876</v>
+        <v>0.416</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>0.0945</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5876</v>
+        <v>0.416</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5876</v>
+        <v>0.4267</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>0.0945</v>
       </c>
       <c r="K86" t="n">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5876</v>
+        <v>0.5212</v>
       </c>
       <c r="N86" t="n">
-        <v>105</v>
+        <v>268</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>xeedo</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5543</v>
+        <v>0.517</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3799</v>
+        <v>0.3543</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.3719</v>
+        <v>-0.3829</v>
       </c>
       <c r="E87" t="n">
-        <v>0.5543</v>
+        <v>0.517</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5543</v>
+        <v>0.6721</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5543</v>
+        <v>0.6721</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5543</v>
+        <v>0.6721</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.5543</v>
+        <v>0.6721</v>
       </c>
       <c r="N87" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>slaxejezzz</t>
+          <t>clax</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5386</v>
+        <v>0.5165</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3691</v>
+        <v>0.354</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.379</v>
+        <v>-0.3831</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5386</v>
+        <v>0.5165</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5386</v>
+        <v>0.3244</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5386</v>
+        <v>0.3244</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5386</v>
+        <v>0.3244</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0.5386</v>
+        <v>0.3244</v>
       </c>
       <c r="N88" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>xelex</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5105</v>
+        <v>0.5038</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3498</v>
+        <v>0.3453</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.3918</v>
+        <v>-0.3888</v>
       </c>
       <c r="E89" t="n">
-        <v>0.5105</v>
+        <v>0.5038</v>
       </c>
       <c r="F89" t="n">
-        <v>0.416</v>
+        <v>0.4846</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0945</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.416</v>
+        <v>0.4846</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4267</v>
+        <v>0.4846</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0945</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="L89" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5212</v>
+        <v>0.4846</v>
       </c>
       <c r="N89" t="n">
-        <v>268</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4846</v>
+        <v>0.4994</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3321</v>
+        <v>0.3422</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.4036</v>
+        <v>-0.3907</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4846</v>
+        <v>0.4994</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4846</v>
+        <v>0.3885</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4846</v>
+        <v>0.3885</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4846</v>
+        <v>0.3885</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0.4846</v>
+        <v>0.3885</v>
       </c>
       <c r="N90" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>xeedo</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.3927</v>
+        <v>0.4931</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2691</v>
+        <v>0.3379</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.4454</v>
+        <v>-0.3936</v>
       </c>
       <c r="E91" t="n">
-        <v>0.3927</v>
+        <v>0.4931</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3927</v>
+        <v>0.5543</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3927</v>
+        <v>0.5543</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3927</v>
+        <v>0.5543</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0.3927</v>
+        <v>0.5543</v>
       </c>
       <c r="N91" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>qw1nk1</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.3885</v>
+        <v>0.4155</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2662</v>
+        <v>0.2847</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.4474</v>
+        <v>-0.4282</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3885</v>
+        <v>0.4155</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3885</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3885</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3885</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0.3885</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="N92" t="n">
-        <v>178</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>slaxejezzz</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.3398</v>
+        <v>0.3931</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2329</v>
+        <v>0.2694</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.4695</v>
+        <v>-0.4382</v>
       </c>
       <c r="E93" t="n">
-        <v>0.3398</v>
+        <v>0.3931</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3398</v>
+        <v>0.5386</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3398</v>
+        <v>0.5386</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3398</v>
+        <v>0.5386</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0.3398</v>
+        <v>0.5386</v>
       </c>
       <c r="N93" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>clax</t>
+          <t>venomzera</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.3244</v>
+        <v>0.2474</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2223</v>
+        <v>0.1695</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.4765</v>
+        <v>-0.5033</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3244</v>
+        <v>0.2474</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3244</v>
+        <v>0.5876</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3244</v>
+        <v>0.5876</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3244</v>
+        <v>0.5876</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0.3244</v>
+        <v>0.5876</v>
       </c>
       <c r="N94" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95">
@@ -4774,16 +4774,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2812</v>
+        <v>0.2161</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1927</v>
+        <v>0.1481</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.4962</v>
+        <v>-0.5173</v>
       </c>
       <c r="E95" t="n">
-        <v>0.2812</v>
+        <v>0.2161</v>
       </c>
       <c r="F95" t="n">
         <v>0.2812</v>
@@ -4816,231 +4816,231 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tikuak</t>
+          <t>sFade8</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2555</v>
+        <v>0.1809</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1751</v>
+        <v>0.124</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.5079</v>
+        <v>-0.533</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2555</v>
+        <v>0.1809</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2555</v>
+        <v>0.2432</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2555</v>
+        <v>0.2432</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2555</v>
+        <v>0.2432</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0.2555</v>
+        <v>0.2432</v>
       </c>
       <c r="N96" t="n">
-        <v>159</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>sFade8</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.2432</v>
+        <v>0.1373</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1667</v>
+        <v>0.0941</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.5135</v>
+        <v>-0.5525</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2432</v>
+        <v>0.1373</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2432</v>
+        <v>-0.1943</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.2432</v>
+        <v>-0.1943</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2432</v>
+        <v>-0.1943</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>204</v>
+        <v>64</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0.2432</v>
+        <v>-0.1943</v>
       </c>
       <c r="N97" t="n">
-        <v>204</v>
+        <v>64</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.224</v>
+        <v>0.1226</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1535</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.5222</v>
+        <v>-0.5591</v>
       </c>
       <c r="E98" t="n">
-        <v>0.224</v>
+        <v>0.1226</v>
       </c>
       <c r="F98" t="n">
-        <v>0.224</v>
+        <v>0.0558</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.224</v>
+        <v>0.0558</v>
       </c>
       <c r="I98" t="n">
-        <v>0.224</v>
+        <v>0.0558</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0.224</v>
+        <v>0.0558</v>
       </c>
       <c r="N98" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.1975</v>
+        <v>0.1188</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1353</v>
+        <v>0.0814</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.5343</v>
+        <v>-0.5608</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1975</v>
+        <v>0.1188</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1975</v>
+        <v>0.224</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1975</v>
+        <v>0.224</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1975</v>
+        <v>0.224</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0.1975</v>
+        <v>0.224</v>
       </c>
       <c r="N99" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.1613</v>
+        <v>0.1129</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1105</v>
+        <v>0.0774</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.5508</v>
+        <v>-0.5634</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1613</v>
+        <v>0.1129</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1613</v>
+        <v>0.3398</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1613</v>
+        <v>0.3398</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1613</v>
+        <v>0.3398</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0.1613</v>
+        <v>0.3398</v>
       </c>
       <c r="N100" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101">
@@ -5050,16 +5050,16 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.1428</v>
+        <v>0.1114</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0979</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.5592</v>
+        <v>-0.5641</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1428</v>
+        <v>0.1114</v>
       </c>
       <c r="F101" t="n">
         <v>0.1428</v>
@@ -5092,584 +5092,584 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>qw1nk1</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1093</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0626</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.5826</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="E102" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1093</v>
       </c>
       <c r="F102" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1975</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1975</v>
       </c>
       <c r="I102" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1975</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1975</v>
       </c>
       <c r="N102" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0589</v>
+        <v>0.109</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0404</v>
+        <v>0.0747</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.5974</v>
+        <v>-0.5651</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0589</v>
+        <v>0.109</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0589</v>
+        <v>0.017</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0589</v>
+        <v>0.017</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0589</v>
+        <v>0.017</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0.0589</v>
+        <v>0.017</v>
       </c>
       <c r="N103" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0558</v>
+        <v>0.105</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0382</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.5988</v>
+        <v>-0.5669</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0558</v>
+        <v>0.105</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0558</v>
+        <v>0.1613</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0558</v>
+        <v>0.1613</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0558</v>
+        <v>0.1613</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0.0558</v>
+        <v>0.1613</v>
       </c>
       <c r="N104" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0552</v>
+        <v>0.0567</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0378</v>
+        <v>0.0389</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.5991</v>
+        <v>-0.5885</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0552</v>
+        <v>0.0567</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0552</v>
+        <v>0.0589</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0552</v>
+        <v>0.0589</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0552</v>
+        <v>0.0589</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0.0552</v>
+        <v>0.0589</v>
       </c>
       <c r="N105" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.017</v>
+        <v>0.0488</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0116</v>
+        <v>0.0334</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.6165</v>
+        <v>-0.592</v>
       </c>
       <c r="E106" t="n">
-        <v>0.017</v>
+        <v>0.0488</v>
       </c>
       <c r="F106" t="n">
-        <v>0.017</v>
+        <v>0.0552</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.017</v>
+        <v>0.0552</v>
       </c>
       <c r="I106" t="n">
-        <v>0.017</v>
+        <v>0.0552</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>0.017</v>
+        <v>0.0552</v>
       </c>
       <c r="N106" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bibu</t>
+          <t>tikuak</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.0266</v>
+        <v>-0.0201</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.0182</v>
+        <v>-0.0138</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.6363</v>
+        <v>-0.6228</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.0266</v>
+        <v>-0.0201</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.0266</v>
+        <v>0.2555</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.0266</v>
+        <v>0.2555</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0266</v>
+        <v>0.2555</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.0266</v>
+        <v>0.2555</v>
       </c>
       <c r="N107" t="n">
-        <v>96</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>Bibu</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.0723</v>
+        <v>-0.1484</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.0495</v>
+        <v>-0.1017</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.6571</v>
+        <v>-0.6801</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.0723</v>
+        <v>-0.1484</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.0723</v>
+        <v>-0.0266</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.0723</v>
+        <v>-0.0266</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0723</v>
+        <v>-0.0266</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.0723</v>
+        <v>-0.0266</v>
       </c>
       <c r="N108" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.0911</v>
+        <v>-0.2158</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.0624</v>
+        <v>-0.1479</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.6657</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0911</v>
+        <v>-0.2158</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3987</v>
+        <v>-0.1917</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.4898</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3987</v>
+        <v>-0.1917</v>
       </c>
       <c r="I109" t="n">
-        <v>0.409</v>
+        <v>-0.1917</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.4898</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="L109" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.08080000000000004</v>
+        <v>-0.1917</v>
       </c>
       <c r="N109" t="n">
-        <v>394</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sinnopsyy</t>
+          <t>AZUWU</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.1006</v>
+        <v>-0.2271</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.0689</v>
+        <v>-0.1556</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.67</v>
+        <v>-0.7153</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.1006</v>
+        <v>-0.2271</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.1006</v>
+        <v>-0.2137</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.1006</v>
+        <v>-0.2137</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1006</v>
+        <v>-0.2137</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-0.1006</v>
+        <v>-0.2137</v>
       </c>
       <c r="N110" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>sinnopsyy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.1275</v>
+        <v>-0.2302</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1578</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.6822</v>
+        <v>-0.7166</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.1275</v>
+        <v>-0.2302</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.1275</v>
+        <v>-0.1006</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.1275</v>
+        <v>-0.1006</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1275</v>
+        <v>-0.1006</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-0.1275</v>
+        <v>-0.1006</v>
       </c>
       <c r="N111" t="n">
-        <v>178</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HexT</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.1291</v>
+        <v>-0.2377</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.0885</v>
+        <v>-0.1629</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.1291</v>
+        <v>-0.2377</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.1291</v>
+        <v>-0.0723</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.1291</v>
+        <v>-0.0723</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1291</v>
+        <v>-0.0723</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>-0.1291</v>
+        <v>-0.0723</v>
       </c>
       <c r="N112" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.1652</v>
+        <v>-0.2391</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.1132</v>
+        <v>-0.1639</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.6994</v>
+        <v>-0.7206</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.1652</v>
+        <v>-0.2391</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.1652</v>
+        <v>-0.3052</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.1652</v>
+        <v>-0.3052</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1652</v>
+        <v>-0.3052</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-0.1652</v>
+        <v>-0.3052</v>
       </c>
       <c r="N113" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.1917</v>
+        <v>-0.2691</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.1314</v>
+        <v>-0.1844</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.7115</v>
+        <v>-0.734</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.1917</v>
+        <v>-0.2691</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.1917</v>
+        <v>-0.3505</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.1917</v>
+        <v>-0.3505</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1917</v>
+        <v>-0.3505</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.1917</v>
+        <v>-0.3505</v>
       </c>
       <c r="N114" t="n">
         <v>87</v>
@@ -5690,262 +5690,262 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.1943</v>
+        <v>-0.2766</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.1332</v>
+        <v>-0.1896</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.7127</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.1943</v>
+        <v>-0.2766</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.1943</v>
+        <v>-0.2298</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.1943</v>
+        <v>-0.2298</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1943</v>
+        <v>-0.2298</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.1943</v>
+        <v>-0.2298</v>
       </c>
       <c r="N115" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AZUWU</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-0.2137</v>
+        <v>-0.2823</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.1464</v>
+        <v>-0.1935</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.7215</v>
+        <v>-0.7399</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.2137</v>
+        <v>-0.2823</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.2137</v>
+        <v>-0.3706</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.2137</v>
+        <v>-0.3706</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2137</v>
+        <v>-0.3706</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.2137</v>
+        <v>-0.3706</v>
       </c>
       <c r="N116" t="n">
-        <v>66</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>HexT</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.2226</v>
+        <v>-0.3139</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.1525</v>
+        <v>-0.2151</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.7255</v>
+        <v>-0.754</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.2226</v>
+        <v>-0.3139</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.2226</v>
+        <v>-0.1291</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.2226</v>
+        <v>-0.1291</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.2226</v>
+        <v>-0.1291</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.2226</v>
+        <v>-0.1291</v>
       </c>
       <c r="N117" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.2298</v>
+        <v>-0.3263</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.1575</v>
+        <v>-0.2236</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.7288</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.2298</v>
+        <v>-0.3263</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.2298</v>
+        <v>-0.1652</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.2298</v>
+        <v>-0.1652</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2298</v>
+        <v>-0.1652</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.2298</v>
+        <v>-0.1652</v>
       </c>
       <c r="N118" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>DarkMeister</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.2461</v>
+        <v>-0.3311</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.1687</v>
+        <v>-0.2269</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.7362</v>
+        <v>-0.7617</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.2461</v>
+        <v>-0.3311</v>
       </c>
       <c r="F119" t="n">
-        <v>0.7539</v>
+        <v>-0.3137</v>
       </c>
       <c r="G119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.7539</v>
+        <v>-0.3137</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7733</v>
+        <v>-0.3137</v>
       </c>
       <c r="J119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L119" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.2267</v>
+        <v>-0.3137</v>
       </c>
       <c r="N119" t="n">
-        <v>232</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Gizmy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.2558</v>
+        <v>-0.3737</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.1753</v>
+        <v>-0.2561</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.7406</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.2558</v>
+        <v>-0.3737</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.2558</v>
+        <v>-0.6223</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.2558</v>
+        <v>-0.6223</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2558</v>
+        <v>-0.6223</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>-0.2558</v>
+        <v>-0.6223</v>
       </c>
       <c r="N120" t="n">
         <v>53</v>
@@ -5966,400 +5966,400 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.2575</v>
+        <v>-0.375</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.1765</v>
+        <v>-0.257</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7813</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.2575</v>
+        <v>-0.375</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.2575</v>
+        <v>0.3987</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>-0.4898</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.2575</v>
+        <v>0.3987</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2575</v>
+        <v>0.409</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>-0.4898</v>
       </c>
       <c r="K121" t="n">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="M121" t="n">
-        <v>-0.2575</v>
+        <v>-0.08080000000000004</v>
       </c>
       <c r="N121" t="n">
-        <v>148</v>
+        <v>394</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.3052</v>
+        <v>-0.4065</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.2092</v>
+        <v>-0.2786</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.7631</v>
+        <v>-0.7954</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.3052</v>
+        <v>-0.4065</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.3052</v>
+        <v>-0.2558</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.3052</v>
+        <v>-0.2558</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.3052</v>
+        <v>-0.2558</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.3052</v>
+        <v>-0.2558</v>
       </c>
       <c r="N122" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DarkMeister</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.3137</v>
+        <v>-0.4317</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.215</v>
+        <v>-0.2958</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.767</v>
+        <v>-0.8067</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.3137</v>
+        <v>-0.4317</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.3137</v>
+        <v>-0.2575</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.3137</v>
+        <v>-0.2575</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3137</v>
+        <v>-0.2575</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.3137</v>
+        <v>-0.2575</v>
       </c>
       <c r="N123" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.3505</v>
+        <v>-0.4362</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.2402</v>
+        <v>-0.2989</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.8087</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.3505</v>
+        <v>-0.4362</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.3505</v>
+        <v>-0.1275</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.3505</v>
+        <v>-0.1275</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3505</v>
+        <v>-0.1275</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.3505</v>
+        <v>-0.1275</v>
       </c>
       <c r="N124" t="n">
-        <v>87</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.3706</v>
+        <v>-0.4512</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.254</v>
+        <v>-0.3092</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.7929</v>
+        <v>-0.8154</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.3706</v>
+        <v>-0.4512</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.3706</v>
+        <v>-0.3746</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.3706</v>
+        <v>-0.3746</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3706</v>
+        <v>-0.3746</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.3706</v>
+        <v>-0.3746</v>
       </c>
       <c r="N125" t="n">
-        <v>148</v>
+        <v>61</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.3746</v>
+        <v>-0.453</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.2567</v>
+        <v>-0.3104</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.7947</v>
+        <v>-0.8162</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.3746</v>
+        <v>-0.453</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.3746</v>
+        <v>0.7539</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.3746</v>
+        <v>0.7539</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3746</v>
+        <v>0.7733</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K126" t="n">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.3746</v>
+        <v>-0.2267</v>
       </c>
       <c r="N126" t="n">
-        <v>61</v>
+        <v>232</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>mhL</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.394</v>
+        <v>-0.512</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.27</v>
+        <v>-0.3509</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.8036</v>
+        <v>-0.8425</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.394</v>
+        <v>-0.512</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.394</v>
+        <v>-0.2226</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.394</v>
+        <v>-0.2226</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.394</v>
+        <v>-0.2226</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.394</v>
+        <v>-0.2226</v>
       </c>
       <c r="N127" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>n0te</t>
+          <t>mhL</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.4488</v>
+        <v>-0.5175</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.3076</v>
+        <v>-0.3546</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.8285</v>
+        <v>-0.845</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.4488</v>
+        <v>-0.5175</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.4488</v>
+        <v>-0.394</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.4488</v>
+        <v>-0.394</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.4488</v>
+        <v>-0.394</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.4488</v>
+        <v>-0.394</v>
       </c>
       <c r="N128" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.4593</v>
+        <v>-0.5332</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.3148</v>
+        <v>-0.3654</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.8333</v>
+        <v>-0.852</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.4593</v>
+        <v>-0.5332</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.4593</v>
+        <v>-0.5023</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.4593</v>
+        <v>-0.5023</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4593</v>
+        <v>-0.5023</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -6371,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.4593</v>
+        <v>-0.5023</v>
       </c>
       <c r="N129" t="n">
         <v>61</v>
@@ -6380,32 +6380,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.5023</v>
+        <v>-0.5437</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.3442</v>
+        <v>-0.3726</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.8529</v>
+        <v>-0.8567</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.5023</v>
+        <v>-0.5437</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.5023</v>
+        <v>-0.4593</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-0.5023</v>
+        <v>-0.4593</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5023</v>
+        <v>-0.4593</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.5023</v>
+        <v>-0.4593</v>
       </c>
       <c r="N130" t="n">
         <v>61</v>
@@ -6426,47 +6426,47 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>X5G7V</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.521</v>
+        <v>-0.6092</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.357</v>
+        <v>-0.4175</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.8859</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.521</v>
+        <v>-0.6092</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.521</v>
+        <v>-0.5484</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.521</v>
+        <v>-0.5484</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.521</v>
+        <v>-0.5484</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>-0.521</v>
+        <v>-0.5484</v>
       </c>
       <c r="N131" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="132">
@@ -6476,16 +6476,16 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.538</v>
+        <v>-0.6681</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.3687</v>
+        <v>-0.4578</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.8691</v>
+        <v>-0.9122</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.538</v>
+        <v>-0.6681</v>
       </c>
       <c r="F132" t="n">
         <v>-0.538</v>
@@ -6518,921 +6518,921 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>X5G7V</t>
+          <t>m1N1</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.5484</v>
+        <v>-0.7251</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.3758</v>
+        <v>-0.4969</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.8738</v>
+        <v>-0.9377</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.5484</v>
+        <v>-0.7251</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.5484</v>
+        <v>-0.6923</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.5484</v>
+        <v>-0.6923</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.5484</v>
+        <v>-0.6923</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-0.5484</v>
+        <v>-0.6923</v>
       </c>
       <c r="N133" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>d1Ledez</t>
+          <t>n0te</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0.6151</v>
+        <v>-0.7451</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.4215</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.9042</v>
+        <v>-0.9466</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.6151</v>
+        <v>-0.7451</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.6151</v>
+        <v>-0.4488</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.6151</v>
+        <v>-0.4488</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.6151</v>
+        <v>-0.4488</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>-0.6151</v>
+        <v>-0.4488</v>
       </c>
       <c r="N134" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Gizmy</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-0.6223</v>
+        <v>-0.7783</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.4265</v>
+        <v>-0.5334</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.9075</v>
+        <v>-0.9615</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.6223</v>
+        <v>-0.7783</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.6223</v>
+        <v>-0.8458</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.6223</v>
+        <v>-0.8458</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6223</v>
+        <v>-0.8458</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>-0.6223</v>
+        <v>-0.8458</v>
       </c>
       <c r="N135" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>m1N1</t>
+          <t>nEMANHA</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.6923</v>
+        <v>-0.8146</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.4744</v>
+        <v>-0.5582</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.9394</v>
+        <v>-0.9777</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.6923</v>
+        <v>-0.8146</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.6923</v>
+        <v>-0.9175</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.6923</v>
+        <v>-0.9175</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6923</v>
+        <v>-0.9175</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-0.6923</v>
+        <v>-0.9175</v>
       </c>
       <c r="N136" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>d1Ledez</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-0.8012</v>
+        <v>-0.8915</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.5491</v>
+        <v>-0.6109</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.9889</v>
+        <v>-1.012</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.8012</v>
+        <v>-0.8915</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.8012</v>
+        <v>-0.6151</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.8012</v>
+        <v>-0.6151</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.8012</v>
+        <v>-0.6151</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-0.8012</v>
+        <v>-0.6151</v>
       </c>
       <c r="N137" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-0.8267</v>
+        <v>-0.8973</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.5665</v>
+        <v>-0.6149</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.0005</v>
+        <v>-1.0146</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.8267</v>
+        <v>-0.8973</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.8267</v>
+        <v>-0.521</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.8267</v>
+        <v>-0.521</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.8267</v>
+        <v>-0.521</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>-0.8267</v>
+        <v>-0.521</v>
       </c>
       <c r="N138" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>poiii</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.8458</v>
+        <v>-0.9489</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.5796</v>
+        <v>-0.6503</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.0092</v>
+        <v>-1.0377</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.8458</v>
+        <v>-0.9489</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.8458</v>
+        <v>-0.9125</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8458</v>
+        <v>-0.9125</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.8458</v>
+        <v>-0.9125</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-0.8458</v>
+        <v>-0.9125</v>
       </c>
       <c r="N139" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-0.8464</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.58</v>
+        <v>-0.6656</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.0095</v>
+        <v>-1.0477</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.8464</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.8464</v>
+        <v>-0.8012</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.8464</v>
+        <v>-0.8012</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.8464</v>
+        <v>-0.8012</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>-0.8464</v>
+        <v>-0.8012</v>
       </c>
       <c r="N140" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kashl1d</t>
+          <t>sirah</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-0.8955</v>
+        <v>-1.0656</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.6137</v>
+        <v>-0.7302</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.0319</v>
+        <v>-1.0898</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.8955</v>
+        <v>-1.0656</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.8955</v>
+        <v>-1.0636</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.8955</v>
+        <v>-1.0636</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8955</v>
+        <v>-1.0636</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-0.8955</v>
+        <v>-1.0636</v>
       </c>
       <c r="N141" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>poiii</t>
+          <t>gr1ks</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-0.9125</v>
+        <v>-1.0982</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.6253</v>
+        <v>-0.7526</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.0396</v>
+        <v>-1.1044</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.9125</v>
+        <v>-1.0982</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.9125</v>
+        <v>-1.0218</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.9125</v>
+        <v>-1.0218</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.9125</v>
+        <v>-1.0218</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.9125</v>
+        <v>-1.0218</v>
       </c>
       <c r="N142" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>nEMANHA</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-0.9175</v>
+        <v>-1.1236</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.6288</v>
+        <v>-0.77</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.0419</v>
+        <v>-1.1157</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.9175</v>
+        <v>-1.1236</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.9175</v>
+        <v>-0.9544</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.9175</v>
+        <v>-0.9544</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.9175</v>
+        <v>-0.9544</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.9175</v>
+        <v>-0.9544</v>
       </c>
       <c r="N143" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-0.9544</v>
+        <v>-1.1315</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.654</v>
+        <v>-0.7754</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.0587</v>
+        <v>-1.1192</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.9544</v>
+        <v>-1.1315</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.9544</v>
+        <v>-0.8464</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.9544</v>
+        <v>-0.8464</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.9544</v>
+        <v>-0.8464</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>-0.9544</v>
+        <v>-0.8464</v>
       </c>
       <c r="N144" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-0.991</v>
+        <v>-1.1432</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.6791</v>
+        <v>-0.7834</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.0753</v>
+        <v>-1.1245</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.991</v>
+        <v>-1.1432</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.991</v>
+        <v>-0.5454</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>-0.5029</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.991</v>
+        <v>-0.5454</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.991</v>
+        <v>-0.5454</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>-0.5029</v>
       </c>
       <c r="K145" t="n">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M145" t="n">
-        <v>-0.991</v>
+        <v>-1.0483</v>
       </c>
       <c r="N145" t="n">
-        <v>61</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>gr1ks</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-1.0218</v>
+        <v>-1.2032</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.7002</v>
+        <v>-0.8245</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.0893</v>
+        <v>-1.1513</v>
       </c>
       <c r="E146" t="n">
-        <v>-1.0218</v>
+        <v>-1.2032</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.0218</v>
+        <v>-0.8267</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>-1.0218</v>
+        <v>-0.8267</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.0218</v>
+        <v>-0.8267</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>-1.0218</v>
+        <v>-0.8267</v>
       </c>
       <c r="N146" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>kashl1d</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-1.0483</v>
+        <v>-1.229</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.7184</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.1014</v>
+        <v>-1.1628</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.0483</v>
+        <v>-1.229</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.5454</v>
+        <v>-0.8955</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.5029</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.5454</v>
+        <v>-0.8955</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.5454</v>
+        <v>-0.8955</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.5029</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="L147" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>-1.0483</v>
+        <v>-0.8955</v>
       </c>
       <c r="N147" t="n">
-        <v>192</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-1.0493</v>
+        <v>-1.3561</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.7191</v>
+        <v>-0.9293</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.1019</v>
+        <v>-1.2196</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.0493</v>
+        <v>-1.3561</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.0493</v>
+        <v>-1.1159</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>-1.0493</v>
+        <v>-1.1159</v>
       </c>
       <c r="I148" t="n">
-        <v>-1.0493</v>
+        <v>-1.1159</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.0493</v>
+        <v>-1.1159</v>
       </c>
       <c r="N148" t="n">
-        <v>61</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sirah</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-1.0636</v>
+        <v>-1.3726</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.7289</v>
+        <v>-0.9406</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.1084</v>
+        <v>-1.2269</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.0636</v>
+        <v>-1.3726</v>
       </c>
       <c r="F149" t="n">
-        <v>-1.0636</v>
+        <v>-0.991</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>-1.0636</v>
+        <v>-0.991</v>
       </c>
       <c r="I149" t="n">
-        <v>-1.0636</v>
+        <v>-0.991</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>-1.0636</v>
+        <v>-0.991</v>
       </c>
       <c r="N149" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-1.1159</v>
+        <v>-1.3768</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.7647</v>
+        <v>-0.9435</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.1322</v>
+        <v>-1.2288</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.1159</v>
+        <v>-1.3768</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.1159</v>
+        <v>-1.1537</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.1159</v>
+        <v>-1.1537</v>
       </c>
       <c r="I150" t="n">
-        <v>-1.1159</v>
+        <v>-1.1537</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>-1.1159</v>
+        <v>-1.1537</v>
       </c>
       <c r="N150" t="n">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-1.1391</v>
+        <v>-1.3811</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.7806</v>
+        <v>-0.9465</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.1427</v>
+        <v>-1.2307</v>
       </c>
       <c r="E151" t="n">
-        <v>-1.1391</v>
+        <v>-1.3811</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.802</v>
+        <v>-1.0493</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.3371</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.802</v>
+        <v>-1.0493</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.802</v>
+        <v>-1.0493</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.3371</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="L151" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>-1.1391</v>
+        <v>-1.0493</v>
       </c>
       <c r="N151" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-1.1537</v>
+        <v>-1.3858</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.7906</v>
+        <v>-0.9497</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.1494</v>
+        <v>-1.2328</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.1537</v>
+        <v>-1.3858</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.1537</v>
+        <v>-0.802</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>-0.3371</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.1537</v>
+        <v>-0.802</v>
       </c>
       <c r="I152" t="n">
-        <v>-1.1537</v>
+        <v>-0.802</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>-0.3371</v>
       </c>
       <c r="K152" t="n">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.1537</v>
+        <v>-1.1391</v>
       </c>
       <c r="N152" t="n">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="153">
@@ -7442,16 +7442,16 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-1.2864</v>
+        <v>-1.403</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.9615</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.2098</v>
+        <v>-1.2405</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.2864</v>
+        <v>-1.403</v>
       </c>
       <c r="F153" t="n">
         <v>-1.2864</v>
@@ -7484,139 +7484,139 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-1.3361</v>
+        <v>-1.5171</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.9156</v>
+        <v>-1.0397</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.2324</v>
+        <v>-1.2915</v>
       </c>
       <c r="E154" t="n">
-        <v>-1.3361</v>
+        <v>-1.5171</v>
       </c>
       <c r="F154" t="n">
-        <v>-1.3361</v>
+        <v>-1.5498</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.3361</v>
+        <v>-1.5498</v>
       </c>
       <c r="I154" t="n">
-        <v>-1.3361</v>
+        <v>-1.5498</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>-1.3361</v>
+        <v>-1.5498</v>
       </c>
       <c r="N154" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-1.4467</v>
+        <v>-1.5621</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-1.0705</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.2828</v>
+        <v>-1.3116</v>
       </c>
       <c r="E155" t="n">
-        <v>-1.4467</v>
+        <v>-1.5621</v>
       </c>
       <c r="F155" t="n">
-        <v>-1.4467</v>
+        <v>-1.3361</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>-1.4467</v>
+        <v>-1.3361</v>
       </c>
       <c r="I155" t="n">
-        <v>-1.4467</v>
+        <v>-1.3361</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>-1.4467</v>
+        <v>-1.3361</v>
       </c>
       <c r="N155" t="n">
-        <v>159</v>
+        <v>107</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-1.5498</v>
+        <v>-1.7294</v>
       </c>
       <c r="C156" t="n">
-        <v>-1.0621</v>
+        <v>-1.1851</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.3297</v>
+        <v>-1.3863</v>
       </c>
       <c r="E156" t="n">
-        <v>-1.5498</v>
+        <v>-1.7294</v>
       </c>
       <c r="F156" t="n">
-        <v>-1.5498</v>
+        <v>-1.4467</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>-1.5498</v>
+        <v>-1.4467</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.5498</v>
+        <v>-1.4467</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>-1.5498</v>
+        <v>-1.4467</v>
       </c>
       <c r="N156" t="n">
-        <v>92</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157">
@@ -7626,16 +7626,16 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-1.6602</v>
+        <v>-1.9356</v>
       </c>
       <c r="C157" t="n">
-        <v>-1.1377</v>
+        <v>-1.3265</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.38</v>
+        <v>-1.4784</v>
       </c>
       <c r="E157" t="n">
-        <v>-1.6602</v>
+        <v>-1.9356</v>
       </c>
       <c r="F157" t="n">
         <v>-1.6602</v>
@@ -7668,93 +7668,93 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-1.8622</v>
+        <v>-2.2465</v>
       </c>
       <c r="C158" t="n">
-        <v>-1.2762</v>
+        <v>-1.5395</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.4719</v>
+        <v>-1.6173</v>
       </c>
       <c r="E158" t="n">
-        <v>-1.8622</v>
+        <v>-2.2465</v>
       </c>
       <c r="F158" t="n">
-        <v>-1.8622</v>
+        <v>-1.0549</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>-0.9856</v>
       </c>
       <c r="H158" t="n">
-        <v>-1.8622</v>
+        <v>-1.0549</v>
       </c>
       <c r="I158" t="n">
-        <v>-1.8622</v>
+        <v>-1.0821</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>-0.9856</v>
       </c>
       <c r="K158" t="n">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M158" t="n">
-        <v>-1.8622</v>
+        <v>-2.0677</v>
       </c>
       <c r="N158" t="n">
-        <v>117</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-2.0405</v>
+        <v>-2.2655</v>
       </c>
       <c r="C159" t="n">
-        <v>-1.3983</v>
+        <v>-1.5525</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.5531</v>
+        <v>-1.6258</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.0405</v>
+        <v>-2.2655</v>
       </c>
       <c r="F159" t="n">
-        <v>-1.0549</v>
+        <v>-1.8622</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.9856</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>-1.0549</v>
+        <v>-1.8622</v>
       </c>
       <c r="I159" t="n">
-        <v>-1.0821</v>
+        <v>-1.8622</v>
       </c>
       <c r="J159" t="n">
-        <v>-0.9856</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="L159" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>-2.0677</v>
+        <v>-1.8622</v>
       </c>
       <c r="N159" t="n">
-        <v>268</v>
+        <v>117</v>
       </c>
     </row>
     <row r="160">
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-2.0419</v>
+        <v>-2.5136</v>
       </c>
       <c r="C160" t="n">
-        <v>-1.3993</v>
+        <v>-1.7226</v>
       </c>
       <c r="D160" t="n">
-        <v>-1.5537</v>
+        <v>-1.7366</v>
       </c>
       <c r="E160" t="n">
-        <v>-2.0419</v>
+        <v>-2.5136</v>
       </c>
       <c r="F160" t="n">
         <v>-1.2499</v>
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-3.298</v>
+        <v>-3.5644</v>
       </c>
       <c r="C161" t="n">
-        <v>-2.2601</v>
+        <v>-2.4427</v>
       </c>
       <c r="D161" t="n">
-        <v>-2.1255</v>
+        <v>-2.206</v>
       </c>
       <c r="E161" t="n">
-        <v>-3.298</v>
+        <v>-3.5644</v>
       </c>
       <c r="F161" t="n">
         <v>-2.9347</v>
